--- a/InputData/elec/PMCCS/Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/PMCCS/Pol Mandated Cap Const Sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/PMCCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C197DE-B7E1-6440-B03A-8EC4F730B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3F67B2-4FF0-914B-9936-97B86C52BE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -893,26 +893,27 @@
     <xf numFmtId="166" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1143,56 +1144,56 @@
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="41" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44" t="s">
+      <c r="A5" s="40"/>
+      <c r="B5" s="40" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44"/>
-      <c r="B6" s="46" t="s">
+      <c r="A6" s="40"/>
+      <c r="B6" s="42" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="40"/>
     </row>
     <row r="9" spans="1:2" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="43" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="173" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="43" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="232" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="47"/>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="43" t="s">
         <v>171</v>
       </c>
     </row>
@@ -8728,40 +8729,40 @@
       </c>
     </row>
     <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="39" t="s">
+      <c r="B87" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="C87" s="40"/>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="40"/>
-      <c r="I87" s="40"/>
-      <c r="J87" s="40"/>
-      <c r="K87" s="40"/>
-      <c r="L87" s="40"/>
-      <c r="M87" s="40"/>
-      <c r="N87" s="40"/>
-      <c r="O87" s="40"/>
-      <c r="P87" s="40"/>
-      <c r="Q87" s="40"/>
-      <c r="R87" s="40"/>
-      <c r="S87" s="40"/>
-      <c r="T87" s="40"/>
-      <c r="U87" s="40"/>
-      <c r="V87" s="40"/>
-      <c r="W87" s="40"/>
-      <c r="X87" s="40"/>
-      <c r="Y87" s="40"/>
-      <c r="Z87" s="40"/>
-      <c r="AA87" s="40"/>
-      <c r="AB87" s="40"/>
-      <c r="AC87" s="40"/>
-      <c r="AD87" s="40"/>
-      <c r="AE87" s="40"/>
-      <c r="AF87" s="40"/>
-      <c r="AG87" s="40"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="49"/>
+      <c r="K87" s="49"/>
+      <c r="L87" s="49"/>
+      <c r="M87" s="49"/>
+      <c r="N87" s="49"/>
+      <c r="O87" s="49"/>
+      <c r="P87" s="49"/>
+      <c r="Q87" s="49"/>
+      <c r="R87" s="49"/>
+      <c r="S87" s="49"/>
+      <c r="T87" s="49"/>
+      <c r="U87" s="49"/>
+      <c r="V87" s="49"/>
+      <c r="W87" s="49"/>
+      <c r="X87" s="49"/>
+      <c r="Y87" s="49"/>
+      <c r="Z87" s="49"/>
+      <c r="AA87" s="49"/>
+      <c r="AB87" s="49"/>
+      <c r="AC87" s="49"/>
+      <c r="AD87" s="49"/>
+      <c r="AE87" s="49"/>
+      <c r="AF87" s="49"/>
+      <c r="AG87" s="49"/>
       <c r="AH87" s="22"/>
     </row>
     <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8885,39 +8886,39 @@
       </c>
     </row>
     <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="41"/>
-      <c r="C112" s="42"/>
-      <c r="D112" s="42"/>
-      <c r="E112" s="42"/>
-      <c r="F112" s="42"/>
-      <c r="G112" s="42"/>
-      <c r="H112" s="42"/>
-      <c r="I112" s="42"/>
-      <c r="J112" s="42"/>
-      <c r="K112" s="42"/>
-      <c r="L112" s="42"/>
-      <c r="M112" s="42"/>
-      <c r="N112" s="42"/>
-      <c r="O112" s="42"/>
-      <c r="P112" s="42"/>
-      <c r="Q112" s="42"/>
-      <c r="R112" s="42"/>
-      <c r="S112" s="42"/>
-      <c r="T112" s="42"/>
-      <c r="U112" s="42"/>
-      <c r="V112" s="42"/>
-      <c r="W112" s="42"/>
-      <c r="X112" s="42"/>
-      <c r="Y112" s="42"/>
-      <c r="Z112" s="42"/>
-      <c r="AA112" s="42"/>
-      <c r="AB112" s="42"/>
-      <c r="AC112" s="42"/>
-      <c r="AD112" s="42"/>
-      <c r="AE112" s="42"/>
-      <c r="AF112" s="42"/>
-      <c r="AG112" s="42"/>
-      <c r="AH112" s="42"/>
+      <c r="B112" s="50"/>
+      <c r="C112" s="51"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="51"/>
+      <c r="F112" s="51"/>
+      <c r="G112" s="51"/>
+      <c r="H112" s="51"/>
+      <c r="I112" s="51"/>
+      <c r="J112" s="51"/>
+      <c r="K112" s="51"/>
+      <c r="L112" s="51"/>
+      <c r="M112" s="51"/>
+      <c r="N112" s="51"/>
+      <c r="O112" s="51"/>
+      <c r="P112" s="51"/>
+      <c r="Q112" s="51"/>
+      <c r="R112" s="51"/>
+      <c r="S112" s="51"/>
+      <c r="T112" s="51"/>
+      <c r="U112" s="51"/>
+      <c r="V112" s="51"/>
+      <c r="W112" s="51"/>
+      <c r="X112" s="51"/>
+      <c r="Y112" s="51"/>
+      <c r="Z112" s="51"/>
+      <c r="AA112" s="51"/>
+      <c r="AB112" s="51"/>
+      <c r="AC112" s="51"/>
+      <c r="AD112" s="51"/>
+      <c r="AE112" s="51"/>
+      <c r="AF112" s="51"/>
+      <c r="AG112" s="51"/>
+      <c r="AH112" s="51"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9115,39 +9116,39 @@
     <row r="306" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="307" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B308" s="41"/>
-      <c r="C308" s="42"/>
-      <c r="D308" s="42"/>
-      <c r="E308" s="42"/>
-      <c r="F308" s="42"/>
-      <c r="G308" s="42"/>
-      <c r="H308" s="42"/>
-      <c r="I308" s="42"/>
-      <c r="J308" s="42"/>
-      <c r="K308" s="42"/>
-      <c r="L308" s="42"/>
-      <c r="M308" s="42"/>
-      <c r="N308" s="42"/>
-      <c r="O308" s="42"/>
-      <c r="P308" s="42"/>
-      <c r="Q308" s="42"/>
-      <c r="R308" s="42"/>
-      <c r="S308" s="42"/>
-      <c r="T308" s="42"/>
-      <c r="U308" s="42"/>
-      <c r="V308" s="42"/>
-      <c r="W308" s="42"/>
-      <c r="X308" s="42"/>
-      <c r="Y308" s="42"/>
-      <c r="Z308" s="42"/>
-      <c r="AA308" s="42"/>
-      <c r="AB308" s="42"/>
-      <c r="AC308" s="42"/>
-      <c r="AD308" s="42"/>
-      <c r="AE308" s="42"/>
-      <c r="AF308" s="42"/>
-      <c r="AG308" s="42"/>
-      <c r="AH308" s="42"/>
+      <c r="B308" s="50"/>
+      <c r="C308" s="51"/>
+      <c r="D308" s="51"/>
+      <c r="E308" s="51"/>
+      <c r="F308" s="51"/>
+      <c r="G308" s="51"/>
+      <c r="H308" s="51"/>
+      <c r="I308" s="51"/>
+      <c r="J308" s="51"/>
+      <c r="K308" s="51"/>
+      <c r="L308" s="51"/>
+      <c r="M308" s="51"/>
+      <c r="N308" s="51"/>
+      <c r="O308" s="51"/>
+      <c r="P308" s="51"/>
+      <c r="Q308" s="51"/>
+      <c r="R308" s="51"/>
+      <c r="S308" s="51"/>
+      <c r="T308" s="51"/>
+      <c r="U308" s="51"/>
+      <c r="V308" s="51"/>
+      <c r="W308" s="51"/>
+      <c r="X308" s="51"/>
+      <c r="Y308" s="51"/>
+      <c r="Z308" s="51"/>
+      <c r="AA308" s="51"/>
+      <c r="AB308" s="51"/>
+      <c r="AC308" s="51"/>
+      <c r="AD308" s="51"/>
+      <c r="AE308" s="51"/>
+      <c r="AF308" s="51"/>
+      <c r="AG308" s="51"/>
+      <c r="AH308" s="51"/>
     </row>
     <row r="309" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="310" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -13676,1747 +13677,2736 @@
   <sheetPr>
     <tabColor rgb="FF1F497D"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:AZ1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
-    <col min="2" max="7" width="8.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="33" width="8.6640625" customWidth="1"/>
+    <col min="2" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="32" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="50">
-        <v>2019</v>
-      </c>
-      <c r="C1" s="50">
+      <c r="B1" s="45">
         <v>2020</v>
       </c>
-      <c r="D1" s="50">
+      <c r="C1" s="45">
         <v>2021</v>
       </c>
-      <c r="E1" s="50">
+      <c r="D1" s="45">
         <v>2022</v>
       </c>
-      <c r="F1" s="50">
+      <c r="E1" s="45">
         <v>2023</v>
       </c>
-      <c r="G1" s="50">
+      <c r="F1" s="45">
         <v>2024</v>
       </c>
-      <c r="H1" s="50">
+      <c r="G1" s="45">
         <v>2025</v>
       </c>
-      <c r="I1" s="50">
+      <c r="H1" s="45">
         <v>2026</v>
       </c>
-      <c r="J1" s="50">
+      <c r="I1" s="45">
         <v>2027</v>
       </c>
-      <c r="K1" s="50">
+      <c r="J1" s="45">
         <v>2028</v>
       </c>
-      <c r="L1" s="50">
+      <c r="K1" s="45">
         <v>2029</v>
       </c>
-      <c r="M1" s="50">
+      <c r="L1" s="45">
         <v>2030</v>
       </c>
-      <c r="N1" s="50">
+      <c r="M1" s="45">
         <v>2031</v>
       </c>
-      <c r="O1" s="50">
+      <c r="N1" s="45">
         <v>2032</v>
       </c>
-      <c r="P1" s="50">
+      <c r="O1" s="45">
         <v>2033</v>
       </c>
-      <c r="Q1" s="50">
+      <c r="P1" s="45">
         <v>2034</v>
       </c>
-      <c r="R1" s="50">
+      <c r="Q1" s="45">
         <v>2035</v>
       </c>
-      <c r="S1" s="50">
+      <c r="R1" s="45">
         <v>2036</v>
       </c>
-      <c r="T1" s="50">
+      <c r="S1" s="45">
         <v>2037</v>
       </c>
-      <c r="U1" s="50">
+      <c r="T1" s="45">
         <v>2038</v>
       </c>
-      <c r="V1" s="50">
+      <c r="U1" s="45">
         <v>2039</v>
       </c>
-      <c r="W1" s="50">
+      <c r="V1" s="45">
         <v>2040</v>
       </c>
-      <c r="X1" s="50">
+      <c r="W1" s="45">
         <v>2041</v>
       </c>
-      <c r="Y1" s="50">
+      <c r="X1" s="45">
         <v>2042</v>
       </c>
-      <c r="Z1" s="50">
+      <c r="Y1" s="45">
         <v>2043</v>
       </c>
-      <c r="AA1" s="50">
+      <c r="Z1" s="45">
         <v>2044</v>
       </c>
-      <c r="AB1" s="50">
+      <c r="AA1" s="45">
         <v>2045</v>
       </c>
-      <c r="AC1" s="50">
+      <c r="AB1" s="45">
         <v>2046</v>
       </c>
-      <c r="AD1" s="50">
+      <c r="AC1" s="45">
         <v>2047</v>
       </c>
-      <c r="AE1" s="50">
+      <c r="AD1" s="45">
         <v>2048</v>
       </c>
-      <c r="AF1" s="50">
+      <c r="AE1" s="45">
         <v>2049</v>
       </c>
-      <c r="AG1" s="50">
+      <c r="AF1" s="45">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG1" s="46">
+        <f>AF1+1</f>
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="46">
+        <f t="shared" ref="AH1:AZ1" si="0">AG1+1</f>
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="46">
+        <f t="shared" si="0"/>
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="46">
+        <f t="shared" si="0"/>
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="46">
+        <f t="shared" si="0"/>
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="46">
+        <f t="shared" si="0"/>
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="46">
+        <f t="shared" si="0"/>
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="46">
+        <f t="shared" si="0"/>
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="46">
+        <f t="shared" si="0"/>
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="46">
+        <f t="shared" si="0"/>
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="46">
+        <f t="shared" si="0"/>
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="46">
+        <f t="shared" si="0"/>
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="46">
+        <f t="shared" si="0"/>
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="46">
+        <f t="shared" si="0"/>
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="46">
+        <f t="shared" si="0"/>
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="46">
+        <f t="shared" si="0"/>
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="46">
+        <f t="shared" si="0"/>
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="46">
+        <f t="shared" si="0"/>
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="46">
+        <f t="shared" si="0"/>
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="46">
+        <f t="shared" si="0"/>
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="49">
-        <v>27193.88</v>
-      </c>
-      <c r="C2" s="49">
-        <v>27193.88</v>
-      </c>
-      <c r="D2" s="49">
-        <v>26844.720000000001</v>
-      </c>
-      <c r="E2" s="49">
-        <v>27181.7</v>
-      </c>
-      <c r="F2" s="49">
-        <v>27490.259999999995</v>
-      </c>
-      <c r="G2" s="49">
-        <v>24745.7</v>
-      </c>
-      <c r="H2" s="49">
-        <v>25050.2</v>
-      </c>
-      <c r="I2" s="49">
-        <v>25001.48</v>
-      </c>
-      <c r="J2" s="49">
-        <v>24498.04</v>
-      </c>
-      <c r="K2" s="49">
-        <v>24290.98</v>
-      </c>
-      <c r="L2" s="49">
-        <v>24104.22</v>
-      </c>
-      <c r="M2" s="49">
-        <v>0</v>
-      </c>
-      <c r="N2" s="49">
-        <v>0</v>
-      </c>
-      <c r="O2" s="49">
-        <v>0</v>
-      </c>
-      <c r="P2" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="49">
-        <v>0</v>
-      </c>
-      <c r="R2" s="49">
-        <v>0</v>
-      </c>
-      <c r="S2" s="49">
-        <v>0</v>
-      </c>
-      <c r="T2" s="49">
-        <v>0</v>
-      </c>
-      <c r="U2" s="49">
-        <v>0</v>
-      </c>
-      <c r="V2" s="49">
-        <v>0</v>
-      </c>
-      <c r="W2" s="49">
-        <v>0</v>
-      </c>
-      <c r="X2" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="44">
+        <v>0</v>
+      </c>
+      <c r="C2" s="44">
+        <v>0</v>
+      </c>
+      <c r="D2" s="44">
+        <v>0</v>
+      </c>
+      <c r="E2" s="44">
+        <v>0</v>
+      </c>
+      <c r="F2" s="44">
+        <v>0</v>
+      </c>
+      <c r="G2" s="44">
+        <v>0</v>
+      </c>
+      <c r="H2" s="44">
+        <v>0</v>
+      </c>
+      <c r="I2" s="44">
+        <v>0</v>
+      </c>
+      <c r="J2" s="44">
+        <v>0</v>
+      </c>
+      <c r="K2" s="44">
+        <v>0</v>
+      </c>
+      <c r="L2" s="44">
+        <v>0</v>
+      </c>
+      <c r="M2" s="44">
+        <v>0</v>
+      </c>
+      <c r="N2" s="44">
+        <v>0</v>
+      </c>
+      <c r="O2" s="44">
+        <v>0</v>
+      </c>
+      <c r="P2" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="44">
+        <v>0</v>
+      </c>
+      <c r="R2" s="44">
+        <v>0</v>
+      </c>
+      <c r="S2" s="44">
+        <v>0</v>
+      </c>
+      <c r="T2" s="44">
+        <v>0</v>
+      </c>
+      <c r="U2" s="44">
+        <v>0</v>
+      </c>
+      <c r="V2" s="44">
+        <v>0</v>
+      </c>
+      <c r="W2" s="44">
+        <v>0</v>
+      </c>
+      <c r="X2" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="49">
-        <v>6731.4799999999987</v>
-      </c>
-      <c r="C3" s="49">
-        <v>6731.4799999999987</v>
-      </c>
-      <c r="D3" s="49">
-        <v>7312.0600000000013</v>
-      </c>
-      <c r="E3" s="49">
-        <v>7348.6</v>
-      </c>
-      <c r="F3" s="49">
-        <v>7052.22</v>
-      </c>
-      <c r="G3" s="49">
-        <v>6349.84</v>
-      </c>
-      <c r="H3" s="49">
-        <v>6029.1</v>
-      </c>
-      <c r="I3" s="49">
-        <v>6045.34</v>
-      </c>
-      <c r="J3" s="49">
-        <v>6390.44</v>
-      </c>
-      <c r="K3" s="49">
-        <v>6309.24</v>
-      </c>
-      <c r="L3" s="49">
-        <v>6268.64</v>
-      </c>
-      <c r="M3" s="49">
-        <v>0</v>
-      </c>
-      <c r="N3" s="49">
-        <v>0</v>
-      </c>
-      <c r="O3" s="49">
-        <v>0</v>
-      </c>
-      <c r="P3" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="49">
-        <v>0</v>
-      </c>
-      <c r="R3" s="49">
-        <v>0</v>
-      </c>
-      <c r="S3" s="49">
-        <v>0</v>
-      </c>
-      <c r="T3" s="49">
-        <v>0</v>
-      </c>
-      <c r="U3" s="49">
-        <v>0</v>
-      </c>
-      <c r="V3" s="49">
-        <v>0</v>
-      </c>
-      <c r="W3" s="49">
-        <v>0</v>
-      </c>
-      <c r="X3" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="44">
+        <v>0</v>
+      </c>
+      <c r="C3" s="44">
+        <v>0</v>
+      </c>
+      <c r="D3" s="44">
+        <v>0</v>
+      </c>
+      <c r="E3" s="44">
+        <v>0</v>
+      </c>
+      <c r="F3" s="44">
+        <v>0</v>
+      </c>
+      <c r="G3" s="44">
+        <v>0</v>
+      </c>
+      <c r="H3" s="44">
+        <v>0</v>
+      </c>
+      <c r="I3" s="44">
+        <v>0</v>
+      </c>
+      <c r="J3" s="44">
+        <v>0</v>
+      </c>
+      <c r="K3" s="44">
+        <v>0</v>
+      </c>
+      <c r="L3" s="44">
+        <v>0</v>
+      </c>
+      <c r="M3" s="44">
+        <v>0</v>
+      </c>
+      <c r="N3" s="44">
+        <v>0</v>
+      </c>
+      <c r="O3" s="44">
+        <v>0</v>
+      </c>
+      <c r="P3" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="44">
+        <v>0</v>
+      </c>
+      <c r="R3" s="44">
+        <v>0</v>
+      </c>
+      <c r="S3" s="44">
+        <v>0</v>
+      </c>
+      <c r="T3" s="44">
+        <v>0</v>
+      </c>
+      <c r="U3" s="44">
+        <v>0</v>
+      </c>
+      <c r="V3" s="44">
+        <v>0</v>
+      </c>
+      <c r="W3" s="44">
+        <v>0</v>
+      </c>
+      <c r="X3" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="49">
-        <v>0</v>
-      </c>
-      <c r="C4" s="49">
-        <v>0</v>
-      </c>
-      <c r="D4" s="49">
-        <v>0</v>
-      </c>
-      <c r="E4" s="49">
-        <v>0</v>
-      </c>
-      <c r="F4" s="49">
-        <v>0</v>
-      </c>
-      <c r="G4" s="49">
-        <v>0</v>
-      </c>
-      <c r="H4" s="49">
-        <v>0</v>
-      </c>
-      <c r="I4" s="49">
-        <v>0</v>
-      </c>
-      <c r="J4" s="49">
-        <v>0</v>
-      </c>
-      <c r="K4" s="49">
-        <v>0</v>
-      </c>
-      <c r="L4" s="49">
-        <v>0</v>
-      </c>
-      <c r="M4" s="49">
-        <v>0</v>
-      </c>
-      <c r="N4" s="49">
-        <v>0</v>
-      </c>
-      <c r="O4" s="49">
-        <v>0</v>
-      </c>
-      <c r="P4" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="49">
-        <v>0</v>
-      </c>
-      <c r="R4" s="49">
-        <v>0</v>
-      </c>
-      <c r="S4" s="49">
-        <v>0</v>
-      </c>
-      <c r="T4" s="49">
-        <v>0</v>
-      </c>
-      <c r="U4" s="49">
-        <v>0</v>
-      </c>
-      <c r="V4" s="49">
-        <v>0</v>
-      </c>
-      <c r="W4" s="49">
-        <v>0</v>
-      </c>
-      <c r="X4" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="44">
+        <v>0</v>
+      </c>
+      <c r="C4" s="44">
+        <v>0</v>
+      </c>
+      <c r="D4" s="44">
+        <v>0</v>
+      </c>
+      <c r="E4" s="44">
+        <v>0</v>
+      </c>
+      <c r="F4" s="44">
+        <v>0</v>
+      </c>
+      <c r="G4" s="44">
+        <v>0</v>
+      </c>
+      <c r="H4" s="44">
+        <v>0</v>
+      </c>
+      <c r="I4" s="44">
+        <v>0</v>
+      </c>
+      <c r="J4" s="44">
+        <v>0</v>
+      </c>
+      <c r="K4" s="44">
+        <v>0</v>
+      </c>
+      <c r="L4" s="44">
+        <v>0</v>
+      </c>
+      <c r="M4" s="44">
+        <v>0</v>
+      </c>
+      <c r="N4" s="44">
+        <v>0</v>
+      </c>
+      <c r="O4" s="44">
+        <v>0</v>
+      </c>
+      <c r="P4" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="44">
+        <v>0</v>
+      </c>
+      <c r="R4" s="44">
+        <v>0</v>
+      </c>
+      <c r="S4" s="44">
+        <v>0</v>
+      </c>
+      <c r="T4" s="44">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44">
+        <v>0</v>
+      </c>
+      <c r="X4" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B5" s="49">
-        <v>544</v>
-      </c>
-      <c r="C5" s="49">
-        <v>544</v>
-      </c>
-      <c r="D5" s="49">
-        <v>207</v>
-      </c>
-      <c r="E5" s="49">
-        <v>409</v>
-      </c>
-      <c r="F5" s="49">
-        <v>376</v>
-      </c>
-      <c r="G5" s="49">
-        <v>2667</v>
-      </c>
-      <c r="H5" s="49">
-        <v>370</v>
-      </c>
-      <c r="I5" s="49">
-        <v>499</v>
-      </c>
-      <c r="J5" s="49">
-        <v>1613</v>
-      </c>
-      <c r="K5" s="49">
-        <v>1791</v>
-      </c>
-      <c r="L5" s="49">
-        <v>1956</v>
-      </c>
-      <c r="M5" s="49">
-        <v>0</v>
-      </c>
-      <c r="N5" s="49">
-        <v>0</v>
-      </c>
-      <c r="O5" s="49">
-        <v>0</v>
-      </c>
-      <c r="P5" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="49">
-        <v>0</v>
-      </c>
-      <c r="R5" s="49">
-        <v>0</v>
-      </c>
-      <c r="S5" s="49">
-        <v>0</v>
-      </c>
-      <c r="T5" s="49">
-        <v>0</v>
-      </c>
-      <c r="U5" s="49">
-        <v>0</v>
-      </c>
-      <c r="V5" s="49">
-        <v>0</v>
-      </c>
-      <c r="W5" s="49">
-        <v>0</v>
-      </c>
-      <c r="X5" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="44">
+        <v>0</v>
+      </c>
+      <c r="C5" s="44">
+        <v>0</v>
+      </c>
+      <c r="D5" s="44">
+        <v>0</v>
+      </c>
+      <c r="E5" s="44">
+        <v>0</v>
+      </c>
+      <c r="F5" s="44">
+        <v>0</v>
+      </c>
+      <c r="G5" s="44">
+        <v>0</v>
+      </c>
+      <c r="H5" s="44">
+        <v>0</v>
+      </c>
+      <c r="I5" s="44">
+        <v>0</v>
+      </c>
+      <c r="J5" s="44">
+        <v>0</v>
+      </c>
+      <c r="K5" s="44">
+        <v>0</v>
+      </c>
+      <c r="L5" s="44">
+        <v>0</v>
+      </c>
+      <c r="M5" s="44">
+        <v>0</v>
+      </c>
+      <c r="N5" s="44">
+        <v>0</v>
+      </c>
+      <c r="O5" s="44">
+        <v>0</v>
+      </c>
+      <c r="P5" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="44">
+        <v>0</v>
+      </c>
+      <c r="R5" s="44">
+        <v>0</v>
+      </c>
+      <c r="S5" s="44">
+        <v>0</v>
+      </c>
+      <c r="T5" s="44">
+        <v>0</v>
+      </c>
+      <c r="U5" s="44">
+        <v>0</v>
+      </c>
+      <c r="V5" s="44">
+        <v>0</v>
+      </c>
+      <c r="W5" s="44">
+        <v>0</v>
+      </c>
+      <c r="X5" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="49">
-        <v>0</v>
-      </c>
-      <c r="C6" s="49">
-        <v>0</v>
-      </c>
-      <c r="D6" s="49">
-        <v>2</v>
-      </c>
-      <c r="E6" s="49">
-        <v>33</v>
-      </c>
-      <c r="F6" s="49">
-        <v>337</v>
-      </c>
-      <c r="G6" s="49">
-        <v>155</v>
-      </c>
-      <c r="H6" s="49">
-        <v>70</v>
-      </c>
-      <c r="I6" s="49">
-        <v>70</v>
-      </c>
-      <c r="J6" s="49">
-        <v>70</v>
-      </c>
-      <c r="K6" s="49">
-        <v>70</v>
-      </c>
-      <c r="L6" s="49">
-        <v>70</v>
-      </c>
-      <c r="M6" s="49">
-        <v>0</v>
-      </c>
-      <c r="N6" s="49">
-        <v>0</v>
-      </c>
-      <c r="O6" s="49">
-        <v>0</v>
-      </c>
-      <c r="P6" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="49">
-        <v>0</v>
-      </c>
-      <c r="R6" s="49">
-        <v>0</v>
-      </c>
-      <c r="S6" s="49">
-        <v>0</v>
-      </c>
-      <c r="T6" s="49">
-        <v>0</v>
-      </c>
-      <c r="U6" s="49">
-        <v>0</v>
-      </c>
-      <c r="V6" s="49">
-        <v>0</v>
-      </c>
-      <c r="W6" s="49">
-        <v>0</v>
-      </c>
-      <c r="X6" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="44">
+        <v>0</v>
+      </c>
+      <c r="C6" s="44">
+        <v>0</v>
+      </c>
+      <c r="D6" s="44">
+        <v>0</v>
+      </c>
+      <c r="E6" s="44">
+        <v>0</v>
+      </c>
+      <c r="F6" s="44">
+        <v>0</v>
+      </c>
+      <c r="G6" s="44">
+        <v>0</v>
+      </c>
+      <c r="H6" s="44">
+        <v>0</v>
+      </c>
+      <c r="I6" s="44">
+        <v>0</v>
+      </c>
+      <c r="J6" s="44">
+        <v>0</v>
+      </c>
+      <c r="K6" s="44">
+        <v>0</v>
+      </c>
+      <c r="L6" s="44">
+        <v>0</v>
+      </c>
+      <c r="M6" s="44">
+        <v>0</v>
+      </c>
+      <c r="N6" s="44">
+        <v>0</v>
+      </c>
+      <c r="O6" s="44">
+        <v>0</v>
+      </c>
+      <c r="P6" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="44">
+        <v>0</v>
+      </c>
+      <c r="R6" s="44">
+        <v>0</v>
+      </c>
+      <c r="S6" s="44">
+        <v>0</v>
+      </c>
+      <c r="T6" s="44">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44">
+        <v>0</v>
+      </c>
+      <c r="X6" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="49">
-        <v>60</v>
-      </c>
-      <c r="C7" s="49">
-        <v>60</v>
-      </c>
-      <c r="D7" s="49">
-        <v>287</v>
-      </c>
-      <c r="E7" s="49">
-        <v>1308</v>
-      </c>
-      <c r="F7" s="49">
-        <v>624</v>
-      </c>
-      <c r="G7" s="49">
-        <v>1631</v>
-      </c>
-      <c r="H7" s="49">
-        <v>127</v>
-      </c>
-      <c r="I7" s="49">
-        <v>148</v>
-      </c>
-      <c r="J7" s="49">
-        <v>165</v>
-      </c>
-      <c r="K7" s="49">
-        <v>172</v>
-      </c>
-      <c r="L7" s="49">
-        <v>157</v>
-      </c>
-      <c r="M7" s="49">
-        <v>0</v>
-      </c>
-      <c r="N7" s="49">
-        <v>0</v>
-      </c>
-      <c r="O7" s="49">
-        <v>0</v>
-      </c>
-      <c r="P7" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="49">
-        <v>0</v>
-      </c>
-      <c r="R7" s="49">
-        <v>0</v>
-      </c>
-      <c r="S7" s="49">
-        <v>0</v>
-      </c>
-      <c r="T7" s="49">
-        <v>0</v>
-      </c>
-      <c r="U7" s="49">
-        <v>0</v>
-      </c>
-      <c r="V7" s="49">
-        <v>0</v>
-      </c>
-      <c r="W7" s="49">
-        <v>0</v>
-      </c>
-      <c r="X7" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="44">
+        <v>0</v>
+      </c>
+      <c r="C7" s="44">
+        <v>0</v>
+      </c>
+      <c r="D7" s="44">
+        <v>0</v>
+      </c>
+      <c r="E7" s="44">
+        <v>0</v>
+      </c>
+      <c r="F7" s="44">
+        <v>0</v>
+      </c>
+      <c r="G7" s="44">
+        <v>0</v>
+      </c>
+      <c r="H7" s="44">
+        <v>0</v>
+      </c>
+      <c r="I7" s="44">
+        <v>0</v>
+      </c>
+      <c r="J7" s="44">
+        <v>0</v>
+      </c>
+      <c r="K7" s="44">
+        <v>0</v>
+      </c>
+      <c r="L7" s="44">
+        <v>0</v>
+      </c>
+      <c r="M7" s="44">
+        <v>0</v>
+      </c>
+      <c r="N7" s="44">
+        <v>0</v>
+      </c>
+      <c r="O7" s="44">
+        <v>0</v>
+      </c>
+      <c r="P7" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="44">
+        <v>0</v>
+      </c>
+      <c r="R7" s="44">
+        <v>0</v>
+      </c>
+      <c r="S7" s="44">
+        <v>0</v>
+      </c>
+      <c r="T7" s="44">
+        <v>0</v>
+      </c>
+      <c r="U7" s="44">
+        <v>0</v>
+      </c>
+      <c r="V7" s="44">
+        <v>0</v>
+      </c>
+      <c r="W7" s="44">
+        <v>0</v>
+      </c>
+      <c r="X7" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="49">
-        <v>0</v>
-      </c>
-      <c r="C8" s="49">
-        <v>0</v>
-      </c>
-      <c r="D8" s="49">
-        <v>0</v>
-      </c>
-      <c r="E8" s="49">
-        <v>0</v>
-      </c>
-      <c r="F8" s="49">
-        <v>0</v>
-      </c>
-      <c r="G8" s="49">
-        <v>0</v>
-      </c>
-      <c r="H8" s="49">
-        <v>0</v>
-      </c>
-      <c r="I8" s="49">
-        <v>0</v>
-      </c>
-      <c r="J8" s="49">
-        <v>0</v>
-      </c>
-      <c r="K8" s="49">
-        <v>0</v>
-      </c>
-      <c r="L8" s="49">
-        <v>0</v>
-      </c>
-      <c r="M8" s="49">
-        <v>0</v>
-      </c>
-      <c r="N8" s="49">
-        <v>0</v>
-      </c>
-      <c r="O8" s="49">
-        <v>0</v>
-      </c>
-      <c r="P8" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="49">
-        <v>0</v>
-      </c>
-      <c r="R8" s="49">
-        <v>0</v>
-      </c>
-      <c r="S8" s="49">
-        <v>0</v>
-      </c>
-      <c r="T8" s="49">
-        <v>0</v>
-      </c>
-      <c r="U8" s="49">
-        <v>0</v>
-      </c>
-      <c r="V8" s="49">
-        <v>0</v>
-      </c>
-      <c r="W8" s="49">
-        <v>0</v>
-      </c>
-      <c r="X8" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="44">
+        <v>0</v>
+      </c>
+      <c r="C8" s="44">
+        <v>0</v>
+      </c>
+      <c r="D8" s="44">
+        <v>0</v>
+      </c>
+      <c r="E8" s="44">
+        <v>0</v>
+      </c>
+      <c r="F8" s="44">
+        <v>0</v>
+      </c>
+      <c r="G8" s="44">
+        <v>0</v>
+      </c>
+      <c r="H8" s="44">
+        <v>0</v>
+      </c>
+      <c r="I8" s="44">
+        <v>0</v>
+      </c>
+      <c r="J8" s="44">
+        <v>0</v>
+      </c>
+      <c r="K8" s="44">
+        <v>0</v>
+      </c>
+      <c r="L8" s="44">
+        <v>0</v>
+      </c>
+      <c r="M8" s="44">
+        <v>0</v>
+      </c>
+      <c r="N8" s="44">
+        <v>0</v>
+      </c>
+      <c r="O8" s="44">
+        <v>0</v>
+      </c>
+      <c r="P8" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="44">
+        <v>0</v>
+      </c>
+      <c r="R8" s="44">
+        <v>0</v>
+      </c>
+      <c r="S8" s="44">
+        <v>0</v>
+      </c>
+      <c r="T8" s="44">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44">
+        <v>0</v>
+      </c>
+      <c r="X8" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="49">
-        <v>12</v>
-      </c>
-      <c r="C9" s="49">
-        <v>12</v>
-      </c>
-      <c r="D9" s="49">
-        <v>43</v>
-      </c>
-      <c r="E9" s="49">
-        <v>88</v>
-      </c>
-      <c r="F9" s="49">
-        <v>191</v>
-      </c>
-      <c r="G9" s="49">
-        <v>221</v>
-      </c>
-      <c r="H9" s="49">
-        <v>20</v>
-      </c>
-      <c r="I9" s="49">
-        <v>20</v>
-      </c>
-      <c r="J9" s="49">
-        <v>20</v>
-      </c>
-      <c r="K9" s="49">
-        <v>20</v>
-      </c>
-      <c r="L9" s="49">
-        <v>20</v>
-      </c>
-      <c r="M9" s="49">
-        <v>0</v>
-      </c>
-      <c r="N9" s="49">
-        <v>0</v>
-      </c>
-      <c r="O9" s="49">
-        <v>0</v>
-      </c>
-      <c r="P9" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="49">
-        <v>0</v>
-      </c>
-      <c r="R9" s="49">
-        <v>0</v>
-      </c>
-      <c r="S9" s="49">
-        <v>0</v>
-      </c>
-      <c r="T9" s="49">
-        <v>0</v>
-      </c>
-      <c r="U9" s="49">
-        <v>0</v>
-      </c>
-      <c r="V9" s="49">
-        <v>0</v>
-      </c>
-      <c r="W9" s="49">
-        <v>0</v>
-      </c>
-      <c r="X9" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="44">
+        <v>0</v>
+      </c>
+      <c r="C9" s="44">
+        <v>0</v>
+      </c>
+      <c r="D9" s="44">
+        <v>0</v>
+      </c>
+      <c r="E9" s="44">
+        <v>0</v>
+      </c>
+      <c r="F9" s="44">
+        <v>0</v>
+      </c>
+      <c r="G9" s="44">
+        <v>0</v>
+      </c>
+      <c r="H9" s="44">
+        <v>0</v>
+      </c>
+      <c r="I9" s="44">
+        <v>0</v>
+      </c>
+      <c r="J9" s="44">
+        <v>0</v>
+      </c>
+      <c r="K9" s="44">
+        <v>0</v>
+      </c>
+      <c r="L9" s="44">
+        <v>0</v>
+      </c>
+      <c r="M9" s="44">
+        <v>0</v>
+      </c>
+      <c r="N9" s="44">
+        <v>0</v>
+      </c>
+      <c r="O9" s="44">
+        <v>0</v>
+      </c>
+      <c r="P9" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="44">
+        <v>0</v>
+      </c>
+      <c r="R9" s="44">
+        <v>0</v>
+      </c>
+      <c r="S9" s="44">
+        <v>0</v>
+      </c>
+      <c r="T9" s="44">
+        <v>0</v>
+      </c>
+      <c r="U9" s="44">
+        <v>0</v>
+      </c>
+      <c r="V9" s="44">
+        <v>0</v>
+      </c>
+      <c r="W9" s="44">
+        <v>0</v>
+      </c>
+      <c r="X9" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="49">
-        <v>136</v>
-      </c>
-      <c r="C10" s="49">
-        <v>136</v>
-      </c>
-      <c r="D10" s="49">
-        <v>108</v>
-      </c>
-      <c r="E10" s="49">
-        <v>190</v>
-      </c>
-      <c r="F10" s="49">
-        <v>141</v>
-      </c>
-      <c r="G10" s="49">
-        <v>870</v>
-      </c>
-      <c r="H10" s="49">
-        <v>290</v>
-      </c>
-      <c r="I10" s="49">
-        <v>123</v>
-      </c>
-      <c r="J10" s="49">
-        <v>450</v>
-      </c>
-      <c r="K10" s="49">
-        <v>240</v>
-      </c>
-      <c r="L10" s="49">
-        <v>808</v>
-      </c>
-      <c r="M10" s="49">
-        <v>0</v>
-      </c>
-      <c r="N10" s="49">
-        <v>0</v>
-      </c>
-      <c r="O10" s="49">
-        <v>0</v>
-      </c>
-      <c r="P10" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="49">
-        <v>0</v>
-      </c>
-      <c r="R10" s="49">
-        <v>0</v>
-      </c>
-      <c r="S10" s="49">
-        <v>0</v>
-      </c>
-      <c r="T10" s="49">
-        <v>0</v>
-      </c>
-      <c r="U10" s="49">
-        <v>0</v>
-      </c>
-      <c r="V10" s="49">
-        <v>0</v>
-      </c>
-      <c r="W10" s="49">
-        <v>0</v>
-      </c>
-      <c r="X10" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="44">
+        <v>0</v>
+      </c>
+      <c r="C10" s="44">
+        <v>0</v>
+      </c>
+      <c r="D10" s="44">
+        <v>0</v>
+      </c>
+      <c r="E10" s="44">
+        <v>0</v>
+      </c>
+      <c r="F10" s="44">
+        <v>0</v>
+      </c>
+      <c r="G10" s="44">
+        <v>0</v>
+      </c>
+      <c r="H10" s="44">
+        <v>0</v>
+      </c>
+      <c r="I10" s="44">
+        <v>0</v>
+      </c>
+      <c r="J10" s="44">
+        <v>0</v>
+      </c>
+      <c r="K10" s="44">
+        <v>0</v>
+      </c>
+      <c r="L10" s="44">
+        <v>0</v>
+      </c>
+      <c r="M10" s="44">
+        <v>0</v>
+      </c>
+      <c r="N10" s="44">
+        <v>0</v>
+      </c>
+      <c r="O10" s="44">
+        <v>0</v>
+      </c>
+      <c r="P10" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="44">
+        <v>0</v>
+      </c>
+      <c r="R10" s="44">
+        <v>0</v>
+      </c>
+      <c r="S10" s="44">
+        <v>0</v>
+      </c>
+      <c r="T10" s="44">
+        <v>0</v>
+      </c>
+      <c r="U10" s="44">
+        <v>0</v>
+      </c>
+      <c r="V10" s="44">
+        <v>0</v>
+      </c>
+      <c r="W10" s="44">
+        <v>0</v>
+      </c>
+      <c r="X10" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="49">
-        <v>0</v>
-      </c>
-      <c r="C11" s="49">
-        <v>0</v>
-      </c>
-      <c r="D11" s="49">
-        <v>0</v>
-      </c>
-      <c r="E11" s="49">
-        <v>0</v>
-      </c>
-      <c r="F11" s="49">
-        <v>0</v>
-      </c>
-      <c r="G11" s="49">
-        <v>0</v>
-      </c>
-      <c r="H11" s="49">
-        <v>0</v>
-      </c>
-      <c r="I11" s="49">
-        <v>0</v>
-      </c>
-      <c r="J11" s="49">
-        <v>0</v>
-      </c>
-      <c r="K11" s="49">
-        <v>0</v>
-      </c>
-      <c r="L11" s="49">
-        <v>0</v>
-      </c>
-      <c r="M11" s="49">
-        <v>0</v>
-      </c>
-      <c r="N11" s="49">
-        <v>0</v>
-      </c>
-      <c r="O11" s="49">
-        <v>0</v>
-      </c>
-      <c r="P11" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="49">
-        <v>0</v>
-      </c>
-      <c r="R11" s="49">
-        <v>0</v>
-      </c>
-      <c r="S11" s="49">
-        <v>0</v>
-      </c>
-      <c r="T11" s="49">
-        <v>0</v>
-      </c>
-      <c r="U11" s="49">
-        <v>0</v>
-      </c>
-      <c r="V11" s="49">
-        <v>0</v>
-      </c>
-      <c r="W11" s="49">
-        <v>0</v>
-      </c>
-      <c r="X11" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="44">
+        <v>0</v>
+      </c>
+      <c r="C11" s="44">
+        <v>0</v>
+      </c>
+      <c r="D11" s="44">
+        <v>0</v>
+      </c>
+      <c r="E11" s="44">
+        <v>0</v>
+      </c>
+      <c r="F11" s="44">
+        <v>0</v>
+      </c>
+      <c r="G11" s="44">
+        <v>0</v>
+      </c>
+      <c r="H11" s="44">
+        <v>0</v>
+      </c>
+      <c r="I11" s="44">
+        <v>0</v>
+      </c>
+      <c r="J11" s="44">
+        <v>0</v>
+      </c>
+      <c r="K11" s="44">
+        <v>0</v>
+      </c>
+      <c r="L11" s="44">
+        <v>0</v>
+      </c>
+      <c r="M11" s="44">
+        <v>0</v>
+      </c>
+      <c r="N11" s="44">
+        <v>0</v>
+      </c>
+      <c r="O11" s="44">
+        <v>0</v>
+      </c>
+      <c r="P11" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="44">
+        <v>0</v>
+      </c>
+      <c r="R11" s="44">
+        <v>0</v>
+      </c>
+      <c r="S11" s="44">
+        <v>0</v>
+      </c>
+      <c r="T11" s="44">
+        <v>0</v>
+      </c>
+      <c r="U11" s="44">
+        <v>0</v>
+      </c>
+      <c r="V11" s="44">
+        <v>0</v>
+      </c>
+      <c r="W11" s="44">
+        <v>0</v>
+      </c>
+      <c r="X11" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="49">
-        <v>0</v>
-      </c>
-      <c r="C12" s="49">
-        <v>0</v>
-      </c>
-      <c r="D12" s="49">
-        <v>0</v>
-      </c>
-      <c r="E12" s="49">
-        <v>0</v>
-      </c>
-      <c r="F12" s="49">
-        <v>0</v>
-      </c>
-      <c r="G12" s="49">
-        <v>0</v>
-      </c>
-      <c r="H12" s="49">
-        <v>0</v>
-      </c>
-      <c r="I12" s="49">
-        <v>0</v>
-      </c>
-      <c r="J12" s="49">
-        <v>0</v>
-      </c>
-      <c r="K12" s="49">
-        <v>0</v>
-      </c>
-      <c r="L12" s="49">
-        <v>0</v>
-      </c>
-      <c r="M12" s="49">
-        <v>0</v>
-      </c>
-      <c r="N12" s="49">
-        <v>0</v>
-      </c>
-      <c r="O12" s="49">
-        <v>0</v>
-      </c>
-      <c r="P12" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="49">
-        <v>0</v>
-      </c>
-      <c r="R12" s="49">
-        <v>0</v>
-      </c>
-      <c r="S12" s="49">
-        <v>0</v>
-      </c>
-      <c r="T12" s="49">
-        <v>0</v>
-      </c>
-      <c r="U12" s="49">
-        <v>0</v>
-      </c>
-      <c r="V12" s="49">
-        <v>0</v>
-      </c>
-      <c r="W12" s="49">
-        <v>0</v>
-      </c>
-      <c r="X12" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="44">
+        <v>0</v>
+      </c>
+      <c r="C12" s="44">
+        <v>0</v>
+      </c>
+      <c r="D12" s="44">
+        <v>0</v>
+      </c>
+      <c r="E12" s="44">
+        <v>0</v>
+      </c>
+      <c r="F12" s="44">
+        <v>0</v>
+      </c>
+      <c r="G12" s="44">
+        <v>0</v>
+      </c>
+      <c r="H12" s="44">
+        <v>0</v>
+      </c>
+      <c r="I12" s="44">
+        <v>0</v>
+      </c>
+      <c r="J12" s="44">
+        <v>0</v>
+      </c>
+      <c r="K12" s="44">
+        <v>0</v>
+      </c>
+      <c r="L12" s="44">
+        <v>0</v>
+      </c>
+      <c r="M12" s="44">
+        <v>0</v>
+      </c>
+      <c r="N12" s="44">
+        <v>0</v>
+      </c>
+      <c r="O12" s="44">
+        <v>0</v>
+      </c>
+      <c r="P12" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="44">
+        <v>0</v>
+      </c>
+      <c r="R12" s="44">
+        <v>0</v>
+      </c>
+      <c r="S12" s="44">
+        <v>0</v>
+      </c>
+      <c r="T12" s="44">
+        <v>0</v>
+      </c>
+      <c r="U12" s="44">
+        <v>0</v>
+      </c>
+      <c r="V12" s="44">
+        <v>0</v>
+      </c>
+      <c r="W12" s="44">
+        <v>0</v>
+      </c>
+      <c r="X12" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="49">
-        <v>0</v>
-      </c>
-      <c r="C13" s="49">
-        <v>0</v>
-      </c>
-      <c r="D13" s="49">
-        <v>0</v>
-      </c>
-      <c r="E13" s="49">
-        <v>0</v>
-      </c>
-      <c r="F13" s="49">
-        <v>0</v>
-      </c>
-      <c r="G13" s="49">
-        <v>0</v>
-      </c>
-      <c r="H13" s="49">
-        <v>0</v>
-      </c>
-      <c r="I13" s="49">
-        <v>0</v>
-      </c>
-      <c r="J13" s="49">
-        <v>0</v>
-      </c>
-      <c r="K13" s="49">
-        <v>0</v>
-      </c>
-      <c r="L13" s="49">
-        <v>0</v>
-      </c>
-      <c r="M13" s="49">
-        <v>0</v>
-      </c>
-      <c r="N13" s="49">
-        <v>0</v>
-      </c>
-      <c r="O13" s="49">
-        <v>0</v>
-      </c>
-      <c r="P13" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="49">
-        <v>0</v>
-      </c>
-      <c r="R13" s="49">
-        <v>0</v>
-      </c>
-      <c r="S13" s="49">
-        <v>0</v>
-      </c>
-      <c r="T13" s="49">
-        <v>0</v>
-      </c>
-      <c r="U13" s="49">
-        <v>0</v>
-      </c>
-      <c r="V13" s="49">
-        <v>0</v>
-      </c>
-      <c r="W13" s="49">
-        <v>0</v>
-      </c>
-      <c r="X13" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="44">
+        <v>0</v>
+      </c>
+      <c r="C13" s="44">
+        <v>0</v>
+      </c>
+      <c r="D13" s="44">
+        <v>0</v>
+      </c>
+      <c r="E13" s="44">
+        <v>0</v>
+      </c>
+      <c r="F13" s="44">
+        <v>0</v>
+      </c>
+      <c r="G13" s="44">
+        <v>0</v>
+      </c>
+      <c r="H13" s="44">
+        <v>0</v>
+      </c>
+      <c r="I13" s="44">
+        <v>0</v>
+      </c>
+      <c r="J13" s="44">
+        <v>0</v>
+      </c>
+      <c r="K13" s="44">
+        <v>0</v>
+      </c>
+      <c r="L13" s="44">
+        <v>0</v>
+      </c>
+      <c r="M13" s="44">
+        <v>0</v>
+      </c>
+      <c r="N13" s="44">
+        <v>0</v>
+      </c>
+      <c r="O13" s="44">
+        <v>0</v>
+      </c>
+      <c r="P13" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="44">
+        <v>0</v>
+      </c>
+      <c r="R13" s="44">
+        <v>0</v>
+      </c>
+      <c r="S13" s="44">
+        <v>0</v>
+      </c>
+      <c r="T13" s="44">
+        <v>0</v>
+      </c>
+      <c r="U13" s="44">
+        <v>0</v>
+      </c>
+      <c r="V13" s="44">
+        <v>0</v>
+      </c>
+      <c r="W13" s="44">
+        <v>0</v>
+      </c>
+      <c r="X13" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="49">
-        <v>0</v>
-      </c>
-      <c r="C14" s="49">
-        <v>0</v>
-      </c>
-      <c r="D14" s="49">
-        <v>0</v>
-      </c>
-      <c r="E14" s="49">
-        <v>0</v>
-      </c>
-      <c r="F14" s="49">
-        <v>0</v>
-      </c>
-      <c r="G14" s="49">
-        <v>0</v>
-      </c>
-      <c r="H14" s="49">
-        <v>0</v>
-      </c>
-      <c r="I14" s="49">
-        <v>0</v>
-      </c>
-      <c r="J14" s="49">
-        <v>0</v>
-      </c>
-      <c r="K14" s="49">
-        <v>0</v>
-      </c>
-      <c r="L14" s="49">
-        <v>0</v>
-      </c>
-      <c r="M14" s="49">
-        <v>0</v>
-      </c>
-      <c r="N14" s="49">
-        <v>0</v>
-      </c>
-      <c r="O14" s="49">
-        <v>0</v>
-      </c>
-      <c r="P14" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="49">
-        <v>0</v>
-      </c>
-      <c r="R14" s="49">
-        <v>0</v>
-      </c>
-      <c r="S14" s="49">
-        <v>0</v>
-      </c>
-      <c r="T14" s="49">
-        <v>0</v>
-      </c>
-      <c r="U14" s="49">
-        <v>0</v>
-      </c>
-      <c r="V14" s="49">
-        <v>0</v>
-      </c>
-      <c r="W14" s="49">
-        <v>0</v>
-      </c>
-      <c r="X14" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="44">
+        <v>0</v>
+      </c>
+      <c r="C14" s="44">
+        <v>0</v>
+      </c>
+      <c r="D14" s="44">
+        <v>0</v>
+      </c>
+      <c r="E14" s="44">
+        <v>0</v>
+      </c>
+      <c r="F14" s="44">
+        <v>0</v>
+      </c>
+      <c r="G14" s="44">
+        <v>0</v>
+      </c>
+      <c r="H14" s="44">
+        <v>0</v>
+      </c>
+      <c r="I14" s="44">
+        <v>0</v>
+      </c>
+      <c r="J14" s="44">
+        <v>0</v>
+      </c>
+      <c r="K14" s="44">
+        <v>0</v>
+      </c>
+      <c r="L14" s="44">
+        <v>0</v>
+      </c>
+      <c r="M14" s="44">
+        <v>0</v>
+      </c>
+      <c r="N14" s="44">
+        <v>0</v>
+      </c>
+      <c r="O14" s="44">
+        <v>0</v>
+      </c>
+      <c r="P14" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="44">
+        <v>0</v>
+      </c>
+      <c r="R14" s="44">
+        <v>0</v>
+      </c>
+      <c r="S14" s="44">
+        <v>0</v>
+      </c>
+      <c r="T14" s="44">
+        <v>0</v>
+      </c>
+      <c r="U14" s="44">
+        <v>0</v>
+      </c>
+      <c r="V14" s="44">
+        <v>0</v>
+      </c>
+      <c r="W14" s="44">
+        <v>0</v>
+      </c>
+      <c r="X14" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B15" s="49">
-        <v>1429.12</v>
-      </c>
-      <c r="C15" s="49">
-        <v>1429.12</v>
-      </c>
-      <c r="D15" s="49">
-        <v>1234.24</v>
-      </c>
-      <c r="E15" s="49">
-        <v>617.12</v>
-      </c>
-      <c r="F15" s="49">
-        <v>207.06</v>
-      </c>
-      <c r="G15" s="49">
-        <v>166.46</v>
-      </c>
-      <c r="H15" s="49">
-        <v>166.46</v>
-      </c>
-      <c r="I15" s="49">
-        <v>166.46</v>
-      </c>
-      <c r="J15" s="49">
-        <v>166.46</v>
-      </c>
-      <c r="K15" s="49">
-        <v>162.4</v>
-      </c>
-      <c r="L15" s="49">
-        <v>162.4</v>
-      </c>
-      <c r="M15" s="49">
-        <v>0</v>
-      </c>
-      <c r="N15" s="49">
-        <v>0</v>
-      </c>
-      <c r="O15" s="49">
-        <v>0</v>
-      </c>
-      <c r="P15" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="49">
-        <v>0</v>
-      </c>
-      <c r="R15" s="49">
-        <v>0</v>
-      </c>
-      <c r="S15" s="49">
-        <v>0</v>
-      </c>
-      <c r="T15" s="49">
-        <v>0</v>
-      </c>
-      <c r="U15" s="49">
-        <v>0</v>
-      </c>
-      <c r="V15" s="49">
-        <v>0</v>
-      </c>
-      <c r="W15" s="49">
-        <v>0</v>
-      </c>
-      <c r="X15" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="44">
+        <v>0</v>
+      </c>
+      <c r="C15" s="44">
+        <v>0</v>
+      </c>
+      <c r="D15" s="44">
+        <v>0</v>
+      </c>
+      <c r="E15" s="44">
+        <v>0</v>
+      </c>
+      <c r="F15" s="44">
+        <v>0</v>
+      </c>
+      <c r="G15" s="44">
+        <v>0</v>
+      </c>
+      <c r="H15" s="44">
+        <v>0</v>
+      </c>
+      <c r="I15" s="44">
+        <v>0</v>
+      </c>
+      <c r="J15" s="44">
+        <v>0</v>
+      </c>
+      <c r="K15" s="44">
+        <v>0</v>
+      </c>
+      <c r="L15" s="44">
+        <v>0</v>
+      </c>
+      <c r="M15" s="44">
+        <v>0</v>
+      </c>
+      <c r="N15" s="44">
+        <v>0</v>
+      </c>
+      <c r="O15" s="44">
+        <v>0</v>
+      </c>
+      <c r="P15" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="44">
+        <v>0</v>
+      </c>
+      <c r="R15" s="44">
+        <v>0</v>
+      </c>
+      <c r="S15" s="44">
+        <v>0</v>
+      </c>
+      <c r="T15" s="44">
+        <v>0</v>
+      </c>
+      <c r="U15" s="44">
+        <v>0</v>
+      </c>
+      <c r="V15" s="44">
+        <v>0</v>
+      </c>
+      <c r="W15" s="44">
+        <v>0</v>
+      </c>
+      <c r="X15" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="49">
-        <v>0</v>
-      </c>
-      <c r="C16" s="49">
-        <v>0</v>
-      </c>
-      <c r="D16" s="49">
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <v>0</v>
-      </c>
-      <c r="G16" s="49">
-        <v>0</v>
-      </c>
-      <c r="H16" s="49">
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <v>0</v>
-      </c>
-      <c r="K16" s="49">
-        <v>0</v>
-      </c>
-      <c r="L16" s="49">
-        <v>0</v>
-      </c>
-      <c r="M16" s="49">
-        <v>0</v>
-      </c>
-      <c r="N16" s="49">
-        <v>0</v>
-      </c>
-      <c r="O16" s="49">
-        <v>0</v>
-      </c>
-      <c r="P16" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="49">
-        <v>0</v>
-      </c>
-      <c r="R16" s="49">
-        <v>0</v>
-      </c>
-      <c r="S16" s="49">
-        <v>0</v>
-      </c>
-      <c r="T16" s="49">
-        <v>0</v>
-      </c>
-      <c r="U16" s="49">
-        <v>0</v>
-      </c>
-      <c r="V16" s="49">
-        <v>0</v>
-      </c>
-      <c r="W16" s="49">
-        <v>0</v>
-      </c>
-      <c r="X16" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="44">
+        <v>0</v>
+      </c>
+      <c r="C16" s="44">
+        <v>0</v>
+      </c>
+      <c r="D16" s="44">
+        <v>0</v>
+      </c>
+      <c r="E16" s="44">
+        <v>0</v>
+      </c>
+      <c r="F16" s="44">
+        <v>0</v>
+      </c>
+      <c r="G16" s="44">
+        <v>0</v>
+      </c>
+      <c r="H16" s="44">
+        <v>0</v>
+      </c>
+      <c r="I16" s="44">
+        <v>0</v>
+      </c>
+      <c r="J16" s="44">
+        <v>0</v>
+      </c>
+      <c r="K16" s="44">
+        <v>0</v>
+      </c>
+      <c r="L16" s="44">
+        <v>0</v>
+      </c>
+      <c r="M16" s="44">
+        <v>0</v>
+      </c>
+      <c r="N16" s="44">
+        <v>0</v>
+      </c>
+      <c r="O16" s="44">
+        <v>0</v>
+      </c>
+      <c r="P16" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="44">
+        <v>0</v>
+      </c>
+      <c r="R16" s="44">
+        <v>0</v>
+      </c>
+      <c r="S16" s="44">
+        <v>0</v>
+      </c>
+      <c r="T16" s="44">
+        <v>0</v>
+      </c>
+      <c r="U16" s="44">
+        <v>0</v>
+      </c>
+      <c r="V16" s="44">
+        <v>0</v>
+      </c>
+      <c r="W16" s="44">
+        <v>0</v>
+      </c>
+      <c r="X16" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="49">
-        <v>0</v>
-      </c>
-      <c r="C17" s="49">
-        <v>0</v>
-      </c>
-      <c r="D17" s="49">
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
-        <v>0</v>
-      </c>
-      <c r="F17" s="49">
-        <v>0</v>
-      </c>
-      <c r="G17" s="49">
-        <v>0</v>
-      </c>
-      <c r="H17" s="49">
-        <v>0</v>
-      </c>
-      <c r="I17" s="49">
-        <v>0</v>
-      </c>
-      <c r="J17" s="49">
-        <v>0</v>
-      </c>
-      <c r="K17" s="49">
-        <v>0</v>
-      </c>
-      <c r="L17" s="49">
-        <v>0</v>
-      </c>
-      <c r="M17" s="49">
-        <v>0</v>
-      </c>
-      <c r="N17" s="49">
-        <v>0</v>
-      </c>
-      <c r="O17" s="49">
-        <v>0</v>
-      </c>
-      <c r="P17" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="49">
-        <v>0</v>
-      </c>
-      <c r="R17" s="49">
-        <v>0</v>
-      </c>
-      <c r="S17" s="49">
-        <v>0</v>
-      </c>
-      <c r="T17" s="49">
-        <v>0</v>
-      </c>
-      <c r="U17" s="49">
-        <v>0</v>
-      </c>
-      <c r="V17" s="49">
-        <v>0</v>
-      </c>
-      <c r="W17" s="49">
-        <v>0</v>
-      </c>
-      <c r="X17" s="49">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="49">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="49">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B17" s="44">
+        <v>0</v>
+      </c>
+      <c r="C17" s="44">
+        <v>0</v>
+      </c>
+      <c r="D17" s="44">
+        <v>0</v>
+      </c>
+      <c r="E17" s="44">
+        <v>0</v>
+      </c>
+      <c r="F17" s="44">
+        <v>0</v>
+      </c>
+      <c r="G17" s="44">
+        <v>0</v>
+      </c>
+      <c r="H17" s="44">
+        <v>0</v>
+      </c>
+      <c r="I17" s="44">
+        <v>0</v>
+      </c>
+      <c r="J17" s="44">
+        <v>0</v>
+      </c>
+      <c r="K17" s="44">
+        <v>0</v>
+      </c>
+      <c r="L17" s="44">
+        <v>0</v>
+      </c>
+      <c r="M17" s="44">
+        <v>0</v>
+      </c>
+      <c r="N17" s="44">
+        <v>0</v>
+      </c>
+      <c r="O17" s="44">
+        <v>0</v>
+      </c>
+      <c r="P17" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="44">
+        <v>0</v>
+      </c>
+      <c r="R17" s="44">
+        <v>0</v>
+      </c>
+      <c r="S17" s="44">
+        <v>0</v>
+      </c>
+      <c r="T17" s="44">
+        <v>0</v>
+      </c>
+      <c r="U17" s="44">
+        <v>0</v>
+      </c>
+      <c r="V17" s="44">
+        <v>0</v>
+      </c>
+      <c r="W17" s="44">
+        <v>0</v>
+      </c>
+      <c r="X17" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="44">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/InputData/elec/PMCCS/Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/PMCCS/Pol Mandated Cap Const Sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/PMCCS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3F67B2-4FF0-914B-9936-97B86C52BE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C197DE-B7E1-6440-B03A-8EC4F730B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -893,27 +893,26 @@
     <xf numFmtId="166" fontId="4" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1144,56 +1143,56 @@
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="41" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40"/>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="44"/>
+      <c r="B6" s="46" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
     </row>
     <row r="9" spans="1:2" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="48" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="173" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="48" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="232" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="47"/>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="48" t="s">
         <v>171</v>
       </c>
     </row>
@@ -8729,40 +8728,40 @@
       </c>
     </row>
     <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="48" t="s">
+      <c r="B87" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
-      <c r="J87" s="49"/>
-      <c r="K87" s="49"/>
-      <c r="L87" s="49"/>
-      <c r="M87" s="49"/>
-      <c r="N87" s="49"/>
-      <c r="O87" s="49"/>
-      <c r="P87" s="49"/>
-      <c r="Q87" s="49"/>
-      <c r="R87" s="49"/>
-      <c r="S87" s="49"/>
-      <c r="T87" s="49"/>
-      <c r="U87" s="49"/>
-      <c r="V87" s="49"/>
-      <c r="W87" s="49"/>
-      <c r="X87" s="49"/>
-      <c r="Y87" s="49"/>
-      <c r="Z87" s="49"/>
-      <c r="AA87" s="49"/>
-      <c r="AB87" s="49"/>
-      <c r="AC87" s="49"/>
-      <c r="AD87" s="49"/>
-      <c r="AE87" s="49"/>
-      <c r="AF87" s="49"/>
-      <c r="AG87" s="49"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+      <c r="J87" s="40"/>
+      <c r="K87" s="40"/>
+      <c r="L87" s="40"/>
+      <c r="M87" s="40"/>
+      <c r="N87" s="40"/>
+      <c r="O87" s="40"/>
+      <c r="P87" s="40"/>
+      <c r="Q87" s="40"/>
+      <c r="R87" s="40"/>
+      <c r="S87" s="40"/>
+      <c r="T87" s="40"/>
+      <c r="U87" s="40"/>
+      <c r="V87" s="40"/>
+      <c r="W87" s="40"/>
+      <c r="X87" s="40"/>
+      <c r="Y87" s="40"/>
+      <c r="Z87" s="40"/>
+      <c r="AA87" s="40"/>
+      <c r="AB87" s="40"/>
+      <c r="AC87" s="40"/>
+      <c r="AD87" s="40"/>
+      <c r="AE87" s="40"/>
+      <c r="AF87" s="40"/>
+      <c r="AG87" s="40"/>
       <c r="AH87" s="22"/>
     </row>
     <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8886,39 +8885,39 @@
       </c>
     </row>
     <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="50"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
-      <c r="F112" s="51"/>
-      <c r="G112" s="51"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="51"/>
-      <c r="J112" s="51"/>
-      <c r="K112" s="51"/>
-      <c r="L112" s="51"/>
-      <c r="M112" s="51"/>
-      <c r="N112" s="51"/>
-      <c r="O112" s="51"/>
-      <c r="P112" s="51"/>
-      <c r="Q112" s="51"/>
-      <c r="R112" s="51"/>
-      <c r="S112" s="51"/>
-      <c r="T112" s="51"/>
-      <c r="U112" s="51"/>
-      <c r="V112" s="51"/>
-      <c r="W112" s="51"/>
-      <c r="X112" s="51"/>
-      <c r="Y112" s="51"/>
-      <c r="Z112" s="51"/>
-      <c r="AA112" s="51"/>
-      <c r="AB112" s="51"/>
-      <c r="AC112" s="51"/>
-      <c r="AD112" s="51"/>
-      <c r="AE112" s="51"/>
-      <c r="AF112" s="51"/>
-      <c r="AG112" s="51"/>
-      <c r="AH112" s="51"/>
+      <c r="B112" s="41"/>
+      <c r="C112" s="42"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="42"/>
+      <c r="F112" s="42"/>
+      <c r="G112" s="42"/>
+      <c r="H112" s="42"/>
+      <c r="I112" s="42"/>
+      <c r="J112" s="42"/>
+      <c r="K112" s="42"/>
+      <c r="L112" s="42"/>
+      <c r="M112" s="42"/>
+      <c r="N112" s="42"/>
+      <c r="O112" s="42"/>
+      <c r="P112" s="42"/>
+      <c r="Q112" s="42"/>
+      <c r="R112" s="42"/>
+      <c r="S112" s="42"/>
+      <c r="T112" s="42"/>
+      <c r="U112" s="42"/>
+      <c r="V112" s="42"/>
+      <c r="W112" s="42"/>
+      <c r="X112" s="42"/>
+      <c r="Y112" s="42"/>
+      <c r="Z112" s="42"/>
+      <c r="AA112" s="42"/>
+      <c r="AB112" s="42"/>
+      <c r="AC112" s="42"/>
+      <c r="AD112" s="42"/>
+      <c r="AE112" s="42"/>
+      <c r="AF112" s="42"/>
+      <c r="AG112" s="42"/>
+      <c r="AH112" s="42"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9116,39 +9115,39 @@
     <row r="306" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="307" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B308" s="50"/>
-      <c r="C308" s="51"/>
-      <c r="D308" s="51"/>
-      <c r="E308" s="51"/>
-      <c r="F308" s="51"/>
-      <c r="G308" s="51"/>
-      <c r="H308" s="51"/>
-      <c r="I308" s="51"/>
-      <c r="J308" s="51"/>
-      <c r="K308" s="51"/>
-      <c r="L308" s="51"/>
-      <c r="M308" s="51"/>
-      <c r="N308" s="51"/>
-      <c r="O308" s="51"/>
-      <c r="P308" s="51"/>
-      <c r="Q308" s="51"/>
-      <c r="R308" s="51"/>
-      <c r="S308" s="51"/>
-      <c r="T308" s="51"/>
-      <c r="U308" s="51"/>
-      <c r="V308" s="51"/>
-      <c r="W308" s="51"/>
-      <c r="X308" s="51"/>
-      <c r="Y308" s="51"/>
-      <c r="Z308" s="51"/>
-      <c r="AA308" s="51"/>
-      <c r="AB308" s="51"/>
-      <c r="AC308" s="51"/>
-      <c r="AD308" s="51"/>
-      <c r="AE308" s="51"/>
-      <c r="AF308" s="51"/>
-      <c r="AG308" s="51"/>
-      <c r="AH308" s="51"/>
+      <c r="B308" s="41"/>
+      <c r="C308" s="42"/>
+      <c r="D308" s="42"/>
+      <c r="E308" s="42"/>
+      <c r="F308" s="42"/>
+      <c r="G308" s="42"/>
+      <c r="H308" s="42"/>
+      <c r="I308" s="42"/>
+      <c r="J308" s="42"/>
+      <c r="K308" s="42"/>
+      <c r="L308" s="42"/>
+      <c r="M308" s="42"/>
+      <c r="N308" s="42"/>
+      <c r="O308" s="42"/>
+      <c r="P308" s="42"/>
+      <c r="Q308" s="42"/>
+      <c r="R308" s="42"/>
+      <c r="S308" s="42"/>
+      <c r="T308" s="42"/>
+      <c r="U308" s="42"/>
+      <c r="V308" s="42"/>
+      <c r="W308" s="42"/>
+      <c r="X308" s="42"/>
+      <c r="Y308" s="42"/>
+      <c r="Z308" s="42"/>
+      <c r="AA308" s="42"/>
+      <c r="AB308" s="42"/>
+      <c r="AC308" s="42"/>
+      <c r="AD308" s="42"/>
+      <c r="AE308" s="42"/>
+      <c r="AF308" s="42"/>
+      <c r="AG308" s="42"/>
+      <c r="AH308" s="42"/>
     </row>
     <row r="309" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="310" spans="2:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -13677,2736 +13676,1747 @@
   <sheetPr>
     <tabColor rgb="FF1F497D"/>
   </sheetPr>
-  <dimension ref="A1:AZ1000"/>
+  <dimension ref="A1:AG1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
-    <col min="2" max="6" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5" customWidth="1"/>
-    <col min="8" max="32" width="8.6640625" customWidth="1"/>
+    <col min="2" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="9" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="45">
+      <c r="B1" s="50">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="50">
         <v>2020</v>
       </c>
-      <c r="C1" s="45">
+      <c r="D1" s="50">
         <v>2021</v>
       </c>
-      <c r="D1" s="45">
+      <c r="E1" s="50">
         <v>2022</v>
       </c>
-      <c r="E1" s="45">
+      <c r="F1" s="50">
         <v>2023</v>
       </c>
-      <c r="F1" s="45">
+      <c r="G1" s="50">
         <v>2024</v>
       </c>
-      <c r="G1" s="45">
+      <c r="H1" s="50">
         <v>2025</v>
       </c>
-      <c r="H1" s="45">
+      <c r="I1" s="50">
         <v>2026</v>
       </c>
-      <c r="I1" s="45">
+      <c r="J1" s="50">
         <v>2027</v>
       </c>
-      <c r="J1" s="45">
+      <c r="K1" s="50">
         <v>2028</v>
       </c>
-      <c r="K1" s="45">
+      <c r="L1" s="50">
         <v>2029</v>
       </c>
-      <c r="L1" s="45">
+      <c r="M1" s="50">
         <v>2030</v>
       </c>
-      <c r="M1" s="45">
+      <c r="N1" s="50">
         <v>2031</v>
       </c>
-      <c r="N1" s="45">
+      <c r="O1" s="50">
         <v>2032</v>
       </c>
-      <c r="O1" s="45">
+      <c r="P1" s="50">
         <v>2033</v>
       </c>
-      <c r="P1" s="45">
+      <c r="Q1" s="50">
         <v>2034</v>
       </c>
-      <c r="Q1" s="45">
+      <c r="R1" s="50">
         <v>2035</v>
       </c>
-      <c r="R1" s="45">
+      <c r="S1" s="50">
         <v>2036</v>
       </c>
-      <c r="S1" s="45">
+      <c r="T1" s="50">
         <v>2037</v>
       </c>
-      <c r="T1" s="45">
+      <c r="U1" s="50">
         <v>2038</v>
       </c>
-      <c r="U1" s="45">
+      <c r="V1" s="50">
         <v>2039</v>
       </c>
-      <c r="V1" s="45">
+      <c r="W1" s="50">
         <v>2040</v>
       </c>
-      <c r="W1" s="45">
+      <c r="X1" s="50">
         <v>2041</v>
       </c>
-      <c r="X1" s="45">
+      <c r="Y1" s="50">
         <v>2042</v>
       </c>
-      <c r="Y1" s="45">
+      <c r="Z1" s="50">
         <v>2043</v>
       </c>
-      <c r="Z1" s="45">
+      <c r="AA1" s="50">
         <v>2044</v>
       </c>
-      <c r="AA1" s="45">
+      <c r="AB1" s="50">
         <v>2045</v>
       </c>
-      <c r="AB1" s="45">
+      <c r="AC1" s="50">
         <v>2046</v>
       </c>
-      <c r="AC1" s="45">
+      <c r="AD1" s="50">
         <v>2047</v>
       </c>
-      <c r="AD1" s="45">
+      <c r="AE1" s="50">
         <v>2048</v>
       </c>
-      <c r="AE1" s="45">
+      <c r="AF1" s="50">
         <v>2049</v>
       </c>
-      <c r="AF1" s="45">
+      <c r="AG1" s="50">
         <v>2050</v>
       </c>
-      <c r="AG1" s="46">
-        <f>AF1+1</f>
-        <v>2051</v>
-      </c>
-      <c r="AH1" s="46">
-        <f t="shared" ref="AH1:AZ1" si="0">AG1+1</f>
-        <v>2052</v>
-      </c>
-      <c r="AI1" s="46">
-        <f t="shared" si="0"/>
-        <v>2053</v>
-      </c>
-      <c r="AJ1" s="46">
-        <f t="shared" si="0"/>
-        <v>2054</v>
-      </c>
-      <c r="AK1" s="46">
-        <f t="shared" si="0"/>
-        <v>2055</v>
-      </c>
-      <c r="AL1" s="46">
-        <f t="shared" si="0"/>
-        <v>2056</v>
-      </c>
-      <c r="AM1" s="46">
-        <f t="shared" si="0"/>
-        <v>2057</v>
-      </c>
-      <c r="AN1" s="46">
-        <f t="shared" si="0"/>
-        <v>2058</v>
-      </c>
-      <c r="AO1" s="46">
-        <f t="shared" si="0"/>
-        <v>2059</v>
-      </c>
-      <c r="AP1" s="46">
-        <f t="shared" si="0"/>
-        <v>2060</v>
-      </c>
-      <c r="AQ1" s="46">
-        <f t="shared" si="0"/>
-        <v>2061</v>
-      </c>
-      <c r="AR1" s="46">
-        <f t="shared" si="0"/>
-        <v>2062</v>
-      </c>
-      <c r="AS1" s="46">
-        <f t="shared" si="0"/>
-        <v>2063</v>
-      </c>
-      <c r="AT1" s="46">
-        <f t="shared" si="0"/>
-        <v>2064</v>
-      </c>
-      <c r="AU1" s="46">
-        <f t="shared" si="0"/>
-        <v>2065</v>
-      </c>
-      <c r="AV1" s="46">
-        <f t="shared" si="0"/>
-        <v>2066</v>
-      </c>
-      <c r="AW1" s="46">
-        <f t="shared" si="0"/>
-        <v>2067</v>
-      </c>
-      <c r="AX1" s="46">
-        <f t="shared" si="0"/>
-        <v>2068</v>
-      </c>
-      <c r="AY1" s="46">
-        <f t="shared" si="0"/>
-        <v>2069</v>
-      </c>
-      <c r="AZ1" s="46">
-        <f t="shared" si="0"/>
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="2" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="44">
-        <v>0</v>
-      </c>
-      <c r="C2" s="44">
-        <v>0</v>
-      </c>
-      <c r="D2" s="44">
-        <v>0</v>
-      </c>
-      <c r="E2" s="44">
-        <v>0</v>
-      </c>
-      <c r="F2" s="44">
-        <v>0</v>
-      </c>
-      <c r="G2" s="44">
-        <v>0</v>
-      </c>
-      <c r="H2" s="44">
-        <v>0</v>
-      </c>
-      <c r="I2" s="44">
-        <v>0</v>
-      </c>
-      <c r="J2" s="44">
-        <v>0</v>
-      </c>
-      <c r="K2" s="44">
-        <v>0</v>
-      </c>
-      <c r="L2" s="44">
-        <v>0</v>
-      </c>
-      <c r="M2" s="44">
-        <v>0</v>
-      </c>
-      <c r="N2" s="44">
-        <v>0</v>
-      </c>
-      <c r="O2" s="44">
-        <v>0</v>
-      </c>
-      <c r="P2" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="44">
-        <v>0</v>
-      </c>
-      <c r="R2" s="44">
-        <v>0</v>
-      </c>
-      <c r="S2" s="44">
-        <v>0</v>
-      </c>
-      <c r="T2" s="44">
-        <v>0</v>
-      </c>
-      <c r="U2" s="44">
-        <v>0</v>
-      </c>
-      <c r="V2" s="44">
-        <v>0</v>
-      </c>
-      <c r="W2" s="44">
-        <v>0</v>
-      </c>
-      <c r="X2" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="49">
+        <v>27193.88</v>
+      </c>
+      <c r="C2" s="49">
+        <v>27193.88</v>
+      </c>
+      <c r="D2" s="49">
+        <v>26844.720000000001</v>
+      </c>
+      <c r="E2" s="49">
+        <v>27181.7</v>
+      </c>
+      <c r="F2" s="49">
+        <v>27490.259999999995</v>
+      </c>
+      <c r="G2" s="49">
+        <v>24745.7</v>
+      </c>
+      <c r="H2" s="49">
+        <v>25050.2</v>
+      </c>
+      <c r="I2" s="49">
+        <v>25001.48</v>
+      </c>
+      <c r="J2" s="49">
+        <v>24498.04</v>
+      </c>
+      <c r="K2" s="49">
+        <v>24290.98</v>
+      </c>
+      <c r="L2" s="49">
+        <v>24104.22</v>
+      </c>
+      <c r="M2" s="49">
+        <v>0</v>
+      </c>
+      <c r="N2" s="49">
+        <v>0</v>
+      </c>
+      <c r="O2" s="49">
+        <v>0</v>
+      </c>
+      <c r="P2" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="49">
+        <v>0</v>
+      </c>
+      <c r="R2" s="49">
+        <v>0</v>
+      </c>
+      <c r="S2" s="49">
+        <v>0</v>
+      </c>
+      <c r="T2" s="49">
+        <v>0</v>
+      </c>
+      <c r="U2" s="49">
+        <v>0</v>
+      </c>
+      <c r="V2" s="49">
+        <v>0</v>
+      </c>
+      <c r="W2" s="49">
+        <v>0</v>
+      </c>
+      <c r="X2" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="44">
-        <v>0</v>
-      </c>
-      <c r="C3" s="44">
-        <v>0</v>
-      </c>
-      <c r="D3" s="44">
-        <v>0</v>
-      </c>
-      <c r="E3" s="44">
-        <v>0</v>
-      </c>
-      <c r="F3" s="44">
-        <v>0</v>
-      </c>
-      <c r="G3" s="44">
-        <v>0</v>
-      </c>
-      <c r="H3" s="44">
-        <v>0</v>
-      </c>
-      <c r="I3" s="44">
-        <v>0</v>
-      </c>
-      <c r="J3" s="44">
-        <v>0</v>
-      </c>
-      <c r="K3" s="44">
-        <v>0</v>
-      </c>
-      <c r="L3" s="44">
-        <v>0</v>
-      </c>
-      <c r="M3" s="44">
-        <v>0</v>
-      </c>
-      <c r="N3" s="44">
-        <v>0</v>
-      </c>
-      <c r="O3" s="44">
-        <v>0</v>
-      </c>
-      <c r="P3" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="44">
-        <v>0</v>
-      </c>
-      <c r="R3" s="44">
-        <v>0</v>
-      </c>
-      <c r="S3" s="44">
-        <v>0</v>
-      </c>
-      <c r="T3" s="44">
-        <v>0</v>
-      </c>
-      <c r="U3" s="44">
-        <v>0</v>
-      </c>
-      <c r="V3" s="44">
-        <v>0</v>
-      </c>
-      <c r="W3" s="44">
-        <v>0</v>
-      </c>
-      <c r="X3" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ3" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="49">
+        <v>6731.4799999999987</v>
+      </c>
+      <c r="C3" s="49">
+        <v>6731.4799999999987</v>
+      </c>
+      <c r="D3" s="49">
+        <v>7312.0600000000013</v>
+      </c>
+      <c r="E3" s="49">
+        <v>7348.6</v>
+      </c>
+      <c r="F3" s="49">
+        <v>7052.22</v>
+      </c>
+      <c r="G3" s="49">
+        <v>6349.84</v>
+      </c>
+      <c r="H3" s="49">
+        <v>6029.1</v>
+      </c>
+      <c r="I3" s="49">
+        <v>6045.34</v>
+      </c>
+      <c r="J3" s="49">
+        <v>6390.44</v>
+      </c>
+      <c r="K3" s="49">
+        <v>6309.24</v>
+      </c>
+      <c r="L3" s="49">
+        <v>6268.64</v>
+      </c>
+      <c r="M3" s="49">
+        <v>0</v>
+      </c>
+      <c r="N3" s="49">
+        <v>0</v>
+      </c>
+      <c r="O3" s="49">
+        <v>0</v>
+      </c>
+      <c r="P3" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="49">
+        <v>0</v>
+      </c>
+      <c r="R3" s="49">
+        <v>0</v>
+      </c>
+      <c r="S3" s="49">
+        <v>0</v>
+      </c>
+      <c r="T3" s="49">
+        <v>0</v>
+      </c>
+      <c r="U3" s="49">
+        <v>0</v>
+      </c>
+      <c r="V3" s="49">
+        <v>0</v>
+      </c>
+      <c r="W3" s="49">
+        <v>0</v>
+      </c>
+      <c r="X3" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="44">
-        <v>0</v>
-      </c>
-      <c r="C4" s="44">
-        <v>0</v>
-      </c>
-      <c r="D4" s="44">
-        <v>0</v>
-      </c>
-      <c r="E4" s="44">
-        <v>0</v>
-      </c>
-      <c r="F4" s="44">
-        <v>0</v>
-      </c>
-      <c r="G4" s="44">
-        <v>0</v>
-      </c>
-      <c r="H4" s="44">
-        <v>0</v>
-      </c>
-      <c r="I4" s="44">
-        <v>0</v>
-      </c>
-      <c r="J4" s="44">
-        <v>0</v>
-      </c>
-      <c r="K4" s="44">
-        <v>0</v>
-      </c>
-      <c r="L4" s="44">
-        <v>0</v>
-      </c>
-      <c r="M4" s="44">
-        <v>0</v>
-      </c>
-      <c r="N4" s="44">
-        <v>0</v>
-      </c>
-      <c r="O4" s="44">
-        <v>0</v>
-      </c>
-      <c r="P4" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="44">
-        <v>0</v>
-      </c>
-      <c r="R4" s="44">
-        <v>0</v>
-      </c>
-      <c r="S4" s="44">
-        <v>0</v>
-      </c>
-      <c r="T4" s="44">
-        <v>0</v>
-      </c>
-      <c r="U4" s="44">
-        <v>0</v>
-      </c>
-      <c r="V4" s="44">
-        <v>0</v>
-      </c>
-      <c r="W4" s="44">
-        <v>0</v>
-      </c>
-      <c r="X4" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="49">
+        <v>0</v>
+      </c>
+      <c r="C4" s="49">
+        <v>0</v>
+      </c>
+      <c r="D4" s="49">
+        <v>0</v>
+      </c>
+      <c r="E4" s="49">
+        <v>0</v>
+      </c>
+      <c r="F4" s="49">
+        <v>0</v>
+      </c>
+      <c r="G4" s="49">
+        <v>0</v>
+      </c>
+      <c r="H4" s="49">
+        <v>0</v>
+      </c>
+      <c r="I4" s="49">
+        <v>0</v>
+      </c>
+      <c r="J4" s="49">
+        <v>0</v>
+      </c>
+      <c r="K4" s="49">
+        <v>0</v>
+      </c>
+      <c r="L4" s="49">
+        <v>0</v>
+      </c>
+      <c r="M4" s="49">
+        <v>0</v>
+      </c>
+      <c r="N4" s="49">
+        <v>0</v>
+      </c>
+      <c r="O4" s="49">
+        <v>0</v>
+      </c>
+      <c r="P4" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="49">
+        <v>0</v>
+      </c>
+      <c r="R4" s="49">
+        <v>0</v>
+      </c>
+      <c r="S4" s="49">
+        <v>0</v>
+      </c>
+      <c r="T4" s="49">
+        <v>0</v>
+      </c>
+      <c r="U4" s="49">
+        <v>0</v>
+      </c>
+      <c r="V4" s="49">
+        <v>0</v>
+      </c>
+      <c r="W4" s="49">
+        <v>0</v>
+      </c>
+      <c r="X4" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B5" s="44">
-        <v>0</v>
-      </c>
-      <c r="C5" s="44">
-        <v>0</v>
-      </c>
-      <c r="D5" s="44">
-        <v>0</v>
-      </c>
-      <c r="E5" s="44">
-        <v>0</v>
-      </c>
-      <c r="F5" s="44">
-        <v>0</v>
-      </c>
-      <c r="G5" s="44">
-        <v>0</v>
-      </c>
-      <c r="H5" s="44">
-        <v>0</v>
-      </c>
-      <c r="I5" s="44">
-        <v>0</v>
-      </c>
-      <c r="J5" s="44">
-        <v>0</v>
-      </c>
-      <c r="K5" s="44">
-        <v>0</v>
-      </c>
-      <c r="L5" s="44">
-        <v>0</v>
-      </c>
-      <c r="M5" s="44">
-        <v>0</v>
-      </c>
-      <c r="N5" s="44">
-        <v>0</v>
-      </c>
-      <c r="O5" s="44">
-        <v>0</v>
-      </c>
-      <c r="P5" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="44">
-        <v>0</v>
-      </c>
-      <c r="R5" s="44">
-        <v>0</v>
-      </c>
-      <c r="S5" s="44">
-        <v>0</v>
-      </c>
-      <c r="T5" s="44">
-        <v>0</v>
-      </c>
-      <c r="U5" s="44">
-        <v>0</v>
-      </c>
-      <c r="V5" s="44">
-        <v>0</v>
-      </c>
-      <c r="W5" s="44">
-        <v>0</v>
-      </c>
-      <c r="X5" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY5" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ5" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="49">
+        <v>544</v>
+      </c>
+      <c r="C5" s="49">
+        <v>544</v>
+      </c>
+      <c r="D5" s="49">
+        <v>207</v>
+      </c>
+      <c r="E5" s="49">
+        <v>409</v>
+      </c>
+      <c r="F5" s="49">
+        <v>376</v>
+      </c>
+      <c r="G5" s="49">
+        <v>2667</v>
+      </c>
+      <c r="H5" s="49">
+        <v>370</v>
+      </c>
+      <c r="I5" s="49">
+        <v>499</v>
+      </c>
+      <c r="J5" s="49">
+        <v>1613</v>
+      </c>
+      <c r="K5" s="49">
+        <v>1791</v>
+      </c>
+      <c r="L5" s="49">
+        <v>1956</v>
+      </c>
+      <c r="M5" s="49">
+        <v>0</v>
+      </c>
+      <c r="N5" s="49">
+        <v>0</v>
+      </c>
+      <c r="O5" s="49">
+        <v>0</v>
+      </c>
+      <c r="P5" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="49">
+        <v>0</v>
+      </c>
+      <c r="R5" s="49">
+        <v>0</v>
+      </c>
+      <c r="S5" s="49">
+        <v>0</v>
+      </c>
+      <c r="T5" s="49">
+        <v>0</v>
+      </c>
+      <c r="U5" s="49">
+        <v>0</v>
+      </c>
+      <c r="V5" s="49">
+        <v>0</v>
+      </c>
+      <c r="W5" s="49">
+        <v>0</v>
+      </c>
+      <c r="X5" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="44">
-        <v>0</v>
-      </c>
-      <c r="C6" s="44">
-        <v>0</v>
-      </c>
-      <c r="D6" s="44">
-        <v>0</v>
-      </c>
-      <c r="E6" s="44">
-        <v>0</v>
-      </c>
-      <c r="F6" s="44">
-        <v>0</v>
-      </c>
-      <c r="G6" s="44">
-        <v>0</v>
-      </c>
-      <c r="H6" s="44">
-        <v>0</v>
-      </c>
-      <c r="I6" s="44">
-        <v>0</v>
-      </c>
-      <c r="J6" s="44">
-        <v>0</v>
-      </c>
-      <c r="K6" s="44">
-        <v>0</v>
-      </c>
-      <c r="L6" s="44">
-        <v>0</v>
-      </c>
-      <c r="M6" s="44">
-        <v>0</v>
-      </c>
-      <c r="N6" s="44">
-        <v>0</v>
-      </c>
-      <c r="O6" s="44">
-        <v>0</v>
-      </c>
-      <c r="P6" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="44">
-        <v>0</v>
-      </c>
-      <c r="R6" s="44">
-        <v>0</v>
-      </c>
-      <c r="S6" s="44">
-        <v>0</v>
-      </c>
-      <c r="T6" s="44">
-        <v>0</v>
-      </c>
-      <c r="U6" s="44">
-        <v>0</v>
-      </c>
-      <c r="V6" s="44">
-        <v>0</v>
-      </c>
-      <c r="W6" s="44">
-        <v>0</v>
-      </c>
-      <c r="X6" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY6" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="49">
+        <v>0</v>
+      </c>
+      <c r="C6" s="49">
+        <v>0</v>
+      </c>
+      <c r="D6" s="49">
+        <v>2</v>
+      </c>
+      <c r="E6" s="49">
+        <v>33</v>
+      </c>
+      <c r="F6" s="49">
+        <v>337</v>
+      </c>
+      <c r="G6" s="49">
+        <v>155</v>
+      </c>
+      <c r="H6" s="49">
+        <v>70</v>
+      </c>
+      <c r="I6" s="49">
+        <v>70</v>
+      </c>
+      <c r="J6" s="49">
+        <v>70</v>
+      </c>
+      <c r="K6" s="49">
+        <v>70</v>
+      </c>
+      <c r="L6" s="49">
+        <v>70</v>
+      </c>
+      <c r="M6" s="49">
+        <v>0</v>
+      </c>
+      <c r="N6" s="49">
+        <v>0</v>
+      </c>
+      <c r="O6" s="49">
+        <v>0</v>
+      </c>
+      <c r="P6" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>0</v>
+      </c>
+      <c r="R6" s="49">
+        <v>0</v>
+      </c>
+      <c r="S6" s="49">
+        <v>0</v>
+      </c>
+      <c r="T6" s="49">
+        <v>0</v>
+      </c>
+      <c r="U6" s="49">
+        <v>0</v>
+      </c>
+      <c r="V6" s="49">
+        <v>0</v>
+      </c>
+      <c r="W6" s="49">
+        <v>0</v>
+      </c>
+      <c r="X6" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="44">
-        <v>0</v>
-      </c>
-      <c r="C7" s="44">
-        <v>0</v>
-      </c>
-      <c r="D7" s="44">
-        <v>0</v>
-      </c>
-      <c r="E7" s="44">
-        <v>0</v>
-      </c>
-      <c r="F7" s="44">
-        <v>0</v>
-      </c>
-      <c r="G7" s="44">
-        <v>0</v>
-      </c>
-      <c r="H7" s="44">
-        <v>0</v>
-      </c>
-      <c r="I7" s="44">
-        <v>0</v>
-      </c>
-      <c r="J7" s="44">
-        <v>0</v>
-      </c>
-      <c r="K7" s="44">
-        <v>0</v>
-      </c>
-      <c r="L7" s="44">
-        <v>0</v>
-      </c>
-      <c r="M7" s="44">
-        <v>0</v>
-      </c>
-      <c r="N7" s="44">
-        <v>0</v>
-      </c>
-      <c r="O7" s="44">
-        <v>0</v>
-      </c>
-      <c r="P7" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="44">
-        <v>0</v>
-      </c>
-      <c r="R7" s="44">
-        <v>0</v>
-      </c>
-      <c r="S7" s="44">
-        <v>0</v>
-      </c>
-      <c r="T7" s="44">
-        <v>0</v>
-      </c>
-      <c r="U7" s="44">
-        <v>0</v>
-      </c>
-      <c r="V7" s="44">
-        <v>0</v>
-      </c>
-      <c r="W7" s="44">
-        <v>0</v>
-      </c>
-      <c r="X7" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY7" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="49">
+        <v>60</v>
+      </c>
+      <c r="C7" s="49">
+        <v>60</v>
+      </c>
+      <c r="D7" s="49">
+        <v>287</v>
+      </c>
+      <c r="E7" s="49">
+        <v>1308</v>
+      </c>
+      <c r="F7" s="49">
+        <v>624</v>
+      </c>
+      <c r="G7" s="49">
+        <v>1631</v>
+      </c>
+      <c r="H7" s="49">
+        <v>127</v>
+      </c>
+      <c r="I7" s="49">
+        <v>148</v>
+      </c>
+      <c r="J7" s="49">
+        <v>165</v>
+      </c>
+      <c r="K7" s="49">
+        <v>172</v>
+      </c>
+      <c r="L7" s="49">
+        <v>157</v>
+      </c>
+      <c r="M7" s="49">
+        <v>0</v>
+      </c>
+      <c r="N7" s="49">
+        <v>0</v>
+      </c>
+      <c r="O7" s="49">
+        <v>0</v>
+      </c>
+      <c r="P7" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>0</v>
+      </c>
+      <c r="R7" s="49">
+        <v>0</v>
+      </c>
+      <c r="S7" s="49">
+        <v>0</v>
+      </c>
+      <c r="T7" s="49">
+        <v>0</v>
+      </c>
+      <c r="U7" s="49">
+        <v>0</v>
+      </c>
+      <c r="V7" s="49">
+        <v>0</v>
+      </c>
+      <c r="W7" s="49">
+        <v>0</v>
+      </c>
+      <c r="X7" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="44">
-        <v>0</v>
-      </c>
-      <c r="C8" s="44">
-        <v>0</v>
-      </c>
-      <c r="D8" s="44">
-        <v>0</v>
-      </c>
-      <c r="E8" s="44">
-        <v>0</v>
-      </c>
-      <c r="F8" s="44">
-        <v>0</v>
-      </c>
-      <c r="G8" s="44">
-        <v>0</v>
-      </c>
-      <c r="H8" s="44">
-        <v>0</v>
-      </c>
-      <c r="I8" s="44">
-        <v>0</v>
-      </c>
-      <c r="J8" s="44">
-        <v>0</v>
-      </c>
-      <c r="K8" s="44">
-        <v>0</v>
-      </c>
-      <c r="L8" s="44">
-        <v>0</v>
-      </c>
-      <c r="M8" s="44">
-        <v>0</v>
-      </c>
-      <c r="N8" s="44">
-        <v>0</v>
-      </c>
-      <c r="O8" s="44">
-        <v>0</v>
-      </c>
-      <c r="P8" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="44">
-        <v>0</v>
-      </c>
-      <c r="R8" s="44">
-        <v>0</v>
-      </c>
-      <c r="S8" s="44">
-        <v>0</v>
-      </c>
-      <c r="T8" s="44">
-        <v>0</v>
-      </c>
-      <c r="U8" s="44">
-        <v>0</v>
-      </c>
-      <c r="V8" s="44">
-        <v>0</v>
-      </c>
-      <c r="W8" s="44">
-        <v>0</v>
-      </c>
-      <c r="X8" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY8" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="49">
+        <v>0</v>
+      </c>
+      <c r="C8" s="49">
+        <v>0</v>
+      </c>
+      <c r="D8" s="49">
+        <v>0</v>
+      </c>
+      <c r="E8" s="49">
+        <v>0</v>
+      </c>
+      <c r="F8" s="49">
+        <v>0</v>
+      </c>
+      <c r="G8" s="49">
+        <v>0</v>
+      </c>
+      <c r="H8" s="49">
+        <v>0</v>
+      </c>
+      <c r="I8" s="49">
+        <v>0</v>
+      </c>
+      <c r="J8" s="49">
+        <v>0</v>
+      </c>
+      <c r="K8" s="49">
+        <v>0</v>
+      </c>
+      <c r="L8" s="49">
+        <v>0</v>
+      </c>
+      <c r="M8" s="49">
+        <v>0</v>
+      </c>
+      <c r="N8" s="49">
+        <v>0</v>
+      </c>
+      <c r="O8" s="49">
+        <v>0</v>
+      </c>
+      <c r="P8" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>0</v>
+      </c>
+      <c r="R8" s="49">
+        <v>0</v>
+      </c>
+      <c r="S8" s="49">
+        <v>0</v>
+      </c>
+      <c r="T8" s="49">
+        <v>0</v>
+      </c>
+      <c r="U8" s="49">
+        <v>0</v>
+      </c>
+      <c r="V8" s="49">
+        <v>0</v>
+      </c>
+      <c r="W8" s="49">
+        <v>0</v>
+      </c>
+      <c r="X8" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="44">
-        <v>0</v>
-      </c>
-      <c r="C9" s="44">
-        <v>0</v>
-      </c>
-      <c r="D9" s="44">
-        <v>0</v>
-      </c>
-      <c r="E9" s="44">
-        <v>0</v>
-      </c>
-      <c r="F9" s="44">
-        <v>0</v>
-      </c>
-      <c r="G9" s="44">
-        <v>0</v>
-      </c>
-      <c r="H9" s="44">
-        <v>0</v>
-      </c>
-      <c r="I9" s="44">
-        <v>0</v>
-      </c>
-      <c r="J9" s="44">
-        <v>0</v>
-      </c>
-      <c r="K9" s="44">
-        <v>0</v>
-      </c>
-      <c r="L9" s="44">
-        <v>0</v>
-      </c>
-      <c r="M9" s="44">
-        <v>0</v>
-      </c>
-      <c r="N9" s="44">
-        <v>0</v>
-      </c>
-      <c r="O9" s="44">
-        <v>0</v>
-      </c>
-      <c r="P9" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="44">
-        <v>0</v>
-      </c>
-      <c r="R9" s="44">
-        <v>0</v>
-      </c>
-      <c r="S9" s="44">
-        <v>0</v>
-      </c>
-      <c r="T9" s="44">
-        <v>0</v>
-      </c>
-      <c r="U9" s="44">
-        <v>0</v>
-      </c>
-      <c r="V9" s="44">
-        <v>0</v>
-      </c>
-      <c r="W9" s="44">
-        <v>0</v>
-      </c>
-      <c r="X9" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY9" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="49">
+        <v>12</v>
+      </c>
+      <c r="C9" s="49">
+        <v>12</v>
+      </c>
+      <c r="D9" s="49">
+        <v>43</v>
+      </c>
+      <c r="E9" s="49">
+        <v>88</v>
+      </c>
+      <c r="F9" s="49">
+        <v>191</v>
+      </c>
+      <c r="G9" s="49">
+        <v>221</v>
+      </c>
+      <c r="H9" s="49">
+        <v>20</v>
+      </c>
+      <c r="I9" s="49">
+        <v>20</v>
+      </c>
+      <c r="J9" s="49">
+        <v>20</v>
+      </c>
+      <c r="K9" s="49">
+        <v>20</v>
+      </c>
+      <c r="L9" s="49">
+        <v>20</v>
+      </c>
+      <c r="M9" s="49">
+        <v>0</v>
+      </c>
+      <c r="N9" s="49">
+        <v>0</v>
+      </c>
+      <c r="O9" s="49">
+        <v>0</v>
+      </c>
+      <c r="P9" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49">
+        <v>0</v>
+      </c>
+      <c r="R9" s="49">
+        <v>0</v>
+      </c>
+      <c r="S9" s="49">
+        <v>0</v>
+      </c>
+      <c r="T9" s="49">
+        <v>0</v>
+      </c>
+      <c r="U9" s="49">
+        <v>0</v>
+      </c>
+      <c r="V9" s="49">
+        <v>0</v>
+      </c>
+      <c r="W9" s="49">
+        <v>0</v>
+      </c>
+      <c r="X9" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="44">
-        <v>0</v>
-      </c>
-      <c r="C10" s="44">
-        <v>0</v>
-      </c>
-      <c r="D10" s="44">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44">
-        <v>0</v>
-      </c>
-      <c r="F10" s="44">
-        <v>0</v>
-      </c>
-      <c r="G10" s="44">
-        <v>0</v>
-      </c>
-      <c r="H10" s="44">
-        <v>0</v>
-      </c>
-      <c r="I10" s="44">
-        <v>0</v>
-      </c>
-      <c r="J10" s="44">
-        <v>0</v>
-      </c>
-      <c r="K10" s="44">
-        <v>0</v>
-      </c>
-      <c r="L10" s="44">
-        <v>0</v>
-      </c>
-      <c r="M10" s="44">
-        <v>0</v>
-      </c>
-      <c r="N10" s="44">
-        <v>0</v>
-      </c>
-      <c r="O10" s="44">
-        <v>0</v>
-      </c>
-      <c r="P10" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="44">
-        <v>0</v>
-      </c>
-      <c r="R10" s="44">
-        <v>0</v>
-      </c>
-      <c r="S10" s="44">
-        <v>0</v>
-      </c>
-      <c r="T10" s="44">
-        <v>0</v>
-      </c>
-      <c r="U10" s="44">
-        <v>0</v>
-      </c>
-      <c r="V10" s="44">
-        <v>0</v>
-      </c>
-      <c r="W10" s="44">
-        <v>0</v>
-      </c>
-      <c r="X10" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY10" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="49">
+        <v>136</v>
+      </c>
+      <c r="C10" s="49">
+        <v>136</v>
+      </c>
+      <c r="D10" s="49">
+        <v>108</v>
+      </c>
+      <c r="E10" s="49">
+        <v>190</v>
+      </c>
+      <c r="F10" s="49">
+        <v>141</v>
+      </c>
+      <c r="G10" s="49">
+        <v>870</v>
+      </c>
+      <c r="H10" s="49">
+        <v>290</v>
+      </c>
+      <c r="I10" s="49">
+        <v>123</v>
+      </c>
+      <c r="J10" s="49">
+        <v>450</v>
+      </c>
+      <c r="K10" s="49">
+        <v>240</v>
+      </c>
+      <c r="L10" s="49">
+        <v>808</v>
+      </c>
+      <c r="M10" s="49">
+        <v>0</v>
+      </c>
+      <c r="N10" s="49">
+        <v>0</v>
+      </c>
+      <c r="O10" s="49">
+        <v>0</v>
+      </c>
+      <c r="P10" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49">
+        <v>0</v>
+      </c>
+      <c r="R10" s="49">
+        <v>0</v>
+      </c>
+      <c r="S10" s="49">
+        <v>0</v>
+      </c>
+      <c r="T10" s="49">
+        <v>0</v>
+      </c>
+      <c r="U10" s="49">
+        <v>0</v>
+      </c>
+      <c r="V10" s="49">
+        <v>0</v>
+      </c>
+      <c r="W10" s="49">
+        <v>0</v>
+      </c>
+      <c r="X10" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="44">
-        <v>0</v>
-      </c>
-      <c r="C11" s="44">
-        <v>0</v>
-      </c>
-      <c r="D11" s="44">
-        <v>0</v>
-      </c>
-      <c r="E11" s="44">
-        <v>0</v>
-      </c>
-      <c r="F11" s="44">
-        <v>0</v>
-      </c>
-      <c r="G11" s="44">
-        <v>0</v>
-      </c>
-      <c r="H11" s="44">
-        <v>0</v>
-      </c>
-      <c r="I11" s="44">
-        <v>0</v>
-      </c>
-      <c r="J11" s="44">
-        <v>0</v>
-      </c>
-      <c r="K11" s="44">
-        <v>0</v>
-      </c>
-      <c r="L11" s="44">
-        <v>0</v>
-      </c>
-      <c r="M11" s="44">
-        <v>0</v>
-      </c>
-      <c r="N11" s="44">
-        <v>0</v>
-      </c>
-      <c r="O11" s="44">
-        <v>0</v>
-      </c>
-      <c r="P11" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="44">
-        <v>0</v>
-      </c>
-      <c r="R11" s="44">
-        <v>0</v>
-      </c>
-      <c r="S11" s="44">
-        <v>0</v>
-      </c>
-      <c r="T11" s="44">
-        <v>0</v>
-      </c>
-      <c r="U11" s="44">
-        <v>0</v>
-      </c>
-      <c r="V11" s="44">
-        <v>0</v>
-      </c>
-      <c r="W11" s="44">
-        <v>0</v>
-      </c>
-      <c r="X11" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY11" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="49">
+        <v>0</v>
+      </c>
+      <c r="C11" s="49">
+        <v>0</v>
+      </c>
+      <c r="D11" s="49">
+        <v>0</v>
+      </c>
+      <c r="E11" s="49">
+        <v>0</v>
+      </c>
+      <c r="F11" s="49">
+        <v>0</v>
+      </c>
+      <c r="G11" s="49">
+        <v>0</v>
+      </c>
+      <c r="H11" s="49">
+        <v>0</v>
+      </c>
+      <c r="I11" s="49">
+        <v>0</v>
+      </c>
+      <c r="J11" s="49">
+        <v>0</v>
+      </c>
+      <c r="K11" s="49">
+        <v>0</v>
+      </c>
+      <c r="L11" s="49">
+        <v>0</v>
+      </c>
+      <c r="M11" s="49">
+        <v>0</v>
+      </c>
+      <c r="N11" s="49">
+        <v>0</v>
+      </c>
+      <c r="O11" s="49">
+        <v>0</v>
+      </c>
+      <c r="P11" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="49">
+        <v>0</v>
+      </c>
+      <c r="R11" s="49">
+        <v>0</v>
+      </c>
+      <c r="S11" s="49">
+        <v>0</v>
+      </c>
+      <c r="T11" s="49">
+        <v>0</v>
+      </c>
+      <c r="U11" s="49">
+        <v>0</v>
+      </c>
+      <c r="V11" s="49">
+        <v>0</v>
+      </c>
+      <c r="W11" s="49">
+        <v>0</v>
+      </c>
+      <c r="X11" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="44">
-        <v>0</v>
-      </c>
-      <c r="C12" s="44">
-        <v>0</v>
-      </c>
-      <c r="D12" s="44">
-        <v>0</v>
-      </c>
-      <c r="E12" s="44">
-        <v>0</v>
-      </c>
-      <c r="F12" s="44">
-        <v>0</v>
-      </c>
-      <c r="G12" s="44">
-        <v>0</v>
-      </c>
-      <c r="H12" s="44">
-        <v>0</v>
-      </c>
-      <c r="I12" s="44">
-        <v>0</v>
-      </c>
-      <c r="J12" s="44">
-        <v>0</v>
-      </c>
-      <c r="K12" s="44">
-        <v>0</v>
-      </c>
-      <c r="L12" s="44">
-        <v>0</v>
-      </c>
-      <c r="M12" s="44">
-        <v>0</v>
-      </c>
-      <c r="N12" s="44">
-        <v>0</v>
-      </c>
-      <c r="O12" s="44">
-        <v>0</v>
-      </c>
-      <c r="P12" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="44">
-        <v>0</v>
-      </c>
-      <c r="R12" s="44">
-        <v>0</v>
-      </c>
-      <c r="S12" s="44">
-        <v>0</v>
-      </c>
-      <c r="T12" s="44">
-        <v>0</v>
-      </c>
-      <c r="U12" s="44">
-        <v>0</v>
-      </c>
-      <c r="V12" s="44">
-        <v>0</v>
-      </c>
-      <c r="W12" s="44">
-        <v>0</v>
-      </c>
-      <c r="X12" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="49">
+        <v>0</v>
+      </c>
+      <c r="C12" s="49">
+        <v>0</v>
+      </c>
+      <c r="D12" s="49">
+        <v>0</v>
+      </c>
+      <c r="E12" s="49">
+        <v>0</v>
+      </c>
+      <c r="F12" s="49">
+        <v>0</v>
+      </c>
+      <c r="G12" s="49">
+        <v>0</v>
+      </c>
+      <c r="H12" s="49">
+        <v>0</v>
+      </c>
+      <c r="I12" s="49">
+        <v>0</v>
+      </c>
+      <c r="J12" s="49">
+        <v>0</v>
+      </c>
+      <c r="K12" s="49">
+        <v>0</v>
+      </c>
+      <c r="L12" s="49">
+        <v>0</v>
+      </c>
+      <c r="M12" s="49">
+        <v>0</v>
+      </c>
+      <c r="N12" s="49">
+        <v>0</v>
+      </c>
+      <c r="O12" s="49">
+        <v>0</v>
+      </c>
+      <c r="P12" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="49">
+        <v>0</v>
+      </c>
+      <c r="R12" s="49">
+        <v>0</v>
+      </c>
+      <c r="S12" s="49">
+        <v>0</v>
+      </c>
+      <c r="T12" s="49">
+        <v>0</v>
+      </c>
+      <c r="U12" s="49">
+        <v>0</v>
+      </c>
+      <c r="V12" s="49">
+        <v>0</v>
+      </c>
+      <c r="W12" s="49">
+        <v>0</v>
+      </c>
+      <c r="X12" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="44">
-        <v>0</v>
-      </c>
-      <c r="C13" s="44">
-        <v>0</v>
-      </c>
-      <c r="D13" s="44">
-        <v>0</v>
-      </c>
-      <c r="E13" s="44">
-        <v>0</v>
-      </c>
-      <c r="F13" s="44">
-        <v>0</v>
-      </c>
-      <c r="G13" s="44">
-        <v>0</v>
-      </c>
-      <c r="H13" s="44">
-        <v>0</v>
-      </c>
-      <c r="I13" s="44">
-        <v>0</v>
-      </c>
-      <c r="J13" s="44">
-        <v>0</v>
-      </c>
-      <c r="K13" s="44">
-        <v>0</v>
-      </c>
-      <c r="L13" s="44">
-        <v>0</v>
-      </c>
-      <c r="M13" s="44">
-        <v>0</v>
-      </c>
-      <c r="N13" s="44">
-        <v>0</v>
-      </c>
-      <c r="O13" s="44">
-        <v>0</v>
-      </c>
-      <c r="P13" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="44">
-        <v>0</v>
-      </c>
-      <c r="R13" s="44">
-        <v>0</v>
-      </c>
-      <c r="S13" s="44">
-        <v>0</v>
-      </c>
-      <c r="T13" s="44">
-        <v>0</v>
-      </c>
-      <c r="U13" s="44">
-        <v>0</v>
-      </c>
-      <c r="V13" s="44">
-        <v>0</v>
-      </c>
-      <c r="W13" s="44">
-        <v>0</v>
-      </c>
-      <c r="X13" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY13" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="49">
+        <v>0</v>
+      </c>
+      <c r="C13" s="49">
+        <v>0</v>
+      </c>
+      <c r="D13" s="49">
+        <v>0</v>
+      </c>
+      <c r="E13" s="49">
+        <v>0</v>
+      </c>
+      <c r="F13" s="49">
+        <v>0</v>
+      </c>
+      <c r="G13" s="49">
+        <v>0</v>
+      </c>
+      <c r="H13" s="49">
+        <v>0</v>
+      </c>
+      <c r="I13" s="49">
+        <v>0</v>
+      </c>
+      <c r="J13" s="49">
+        <v>0</v>
+      </c>
+      <c r="K13" s="49">
+        <v>0</v>
+      </c>
+      <c r="L13" s="49">
+        <v>0</v>
+      </c>
+      <c r="M13" s="49">
+        <v>0</v>
+      </c>
+      <c r="N13" s="49">
+        <v>0</v>
+      </c>
+      <c r="O13" s="49">
+        <v>0</v>
+      </c>
+      <c r="P13" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="49">
+        <v>0</v>
+      </c>
+      <c r="R13" s="49">
+        <v>0</v>
+      </c>
+      <c r="S13" s="49">
+        <v>0</v>
+      </c>
+      <c r="T13" s="49">
+        <v>0</v>
+      </c>
+      <c r="U13" s="49">
+        <v>0</v>
+      </c>
+      <c r="V13" s="49">
+        <v>0</v>
+      </c>
+      <c r="W13" s="49">
+        <v>0</v>
+      </c>
+      <c r="X13" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="44">
-        <v>0</v>
-      </c>
-      <c r="C14" s="44">
-        <v>0</v>
-      </c>
-      <c r="D14" s="44">
-        <v>0</v>
-      </c>
-      <c r="E14" s="44">
-        <v>0</v>
-      </c>
-      <c r="F14" s="44">
-        <v>0</v>
-      </c>
-      <c r="G14" s="44">
-        <v>0</v>
-      </c>
-      <c r="H14" s="44">
-        <v>0</v>
-      </c>
-      <c r="I14" s="44">
-        <v>0</v>
-      </c>
-      <c r="J14" s="44">
-        <v>0</v>
-      </c>
-      <c r="K14" s="44">
-        <v>0</v>
-      </c>
-      <c r="L14" s="44">
-        <v>0</v>
-      </c>
-      <c r="M14" s="44">
-        <v>0</v>
-      </c>
-      <c r="N14" s="44">
-        <v>0</v>
-      </c>
-      <c r="O14" s="44">
-        <v>0</v>
-      </c>
-      <c r="P14" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="44">
-        <v>0</v>
-      </c>
-      <c r="R14" s="44">
-        <v>0</v>
-      </c>
-      <c r="S14" s="44">
-        <v>0</v>
-      </c>
-      <c r="T14" s="44">
-        <v>0</v>
-      </c>
-      <c r="U14" s="44">
-        <v>0</v>
-      </c>
-      <c r="V14" s="44">
-        <v>0</v>
-      </c>
-      <c r="W14" s="44">
-        <v>0</v>
-      </c>
-      <c r="X14" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY14" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="49">
+        <v>0</v>
+      </c>
+      <c r="C14" s="49">
+        <v>0</v>
+      </c>
+      <c r="D14" s="49">
+        <v>0</v>
+      </c>
+      <c r="E14" s="49">
+        <v>0</v>
+      </c>
+      <c r="F14" s="49">
+        <v>0</v>
+      </c>
+      <c r="G14" s="49">
+        <v>0</v>
+      </c>
+      <c r="H14" s="49">
+        <v>0</v>
+      </c>
+      <c r="I14" s="49">
+        <v>0</v>
+      </c>
+      <c r="J14" s="49">
+        <v>0</v>
+      </c>
+      <c r="K14" s="49">
+        <v>0</v>
+      </c>
+      <c r="L14" s="49">
+        <v>0</v>
+      </c>
+      <c r="M14" s="49">
+        <v>0</v>
+      </c>
+      <c r="N14" s="49">
+        <v>0</v>
+      </c>
+      <c r="O14" s="49">
+        <v>0</v>
+      </c>
+      <c r="P14" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="49">
+        <v>0</v>
+      </c>
+      <c r="R14" s="49">
+        <v>0</v>
+      </c>
+      <c r="S14" s="49">
+        <v>0</v>
+      </c>
+      <c r="T14" s="49">
+        <v>0</v>
+      </c>
+      <c r="U14" s="49">
+        <v>0</v>
+      </c>
+      <c r="V14" s="49">
+        <v>0</v>
+      </c>
+      <c r="W14" s="49">
+        <v>0</v>
+      </c>
+      <c r="X14" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B15" s="44">
-        <v>0</v>
-      </c>
-      <c r="C15" s="44">
-        <v>0</v>
-      </c>
-      <c r="D15" s="44">
-        <v>0</v>
-      </c>
-      <c r="E15" s="44">
-        <v>0</v>
-      </c>
-      <c r="F15" s="44">
-        <v>0</v>
-      </c>
-      <c r="G15" s="44">
-        <v>0</v>
-      </c>
-      <c r="H15" s="44">
-        <v>0</v>
-      </c>
-      <c r="I15" s="44">
-        <v>0</v>
-      </c>
-      <c r="J15" s="44">
-        <v>0</v>
-      </c>
-      <c r="K15" s="44">
-        <v>0</v>
-      </c>
-      <c r="L15" s="44">
-        <v>0</v>
-      </c>
-      <c r="M15" s="44">
-        <v>0</v>
-      </c>
-      <c r="N15" s="44">
-        <v>0</v>
-      </c>
-      <c r="O15" s="44">
-        <v>0</v>
-      </c>
-      <c r="P15" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="44">
-        <v>0</v>
-      </c>
-      <c r="R15" s="44">
-        <v>0</v>
-      </c>
-      <c r="S15" s="44">
-        <v>0</v>
-      </c>
-      <c r="T15" s="44">
-        <v>0</v>
-      </c>
-      <c r="U15" s="44">
-        <v>0</v>
-      </c>
-      <c r="V15" s="44">
-        <v>0</v>
-      </c>
-      <c r="W15" s="44">
-        <v>0</v>
-      </c>
-      <c r="X15" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY15" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ15" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="49">
+        <v>1429.12</v>
+      </c>
+      <c r="C15" s="49">
+        <v>1429.12</v>
+      </c>
+      <c r="D15" s="49">
+        <v>1234.24</v>
+      </c>
+      <c r="E15" s="49">
+        <v>617.12</v>
+      </c>
+      <c r="F15" s="49">
+        <v>207.06</v>
+      </c>
+      <c r="G15" s="49">
+        <v>166.46</v>
+      </c>
+      <c r="H15" s="49">
+        <v>166.46</v>
+      </c>
+      <c r="I15" s="49">
+        <v>166.46</v>
+      </c>
+      <c r="J15" s="49">
+        <v>166.46</v>
+      </c>
+      <c r="K15" s="49">
+        <v>162.4</v>
+      </c>
+      <c r="L15" s="49">
+        <v>162.4</v>
+      </c>
+      <c r="M15" s="49">
+        <v>0</v>
+      </c>
+      <c r="N15" s="49">
+        <v>0</v>
+      </c>
+      <c r="O15" s="49">
+        <v>0</v>
+      </c>
+      <c r="P15" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="49">
+        <v>0</v>
+      </c>
+      <c r="R15" s="49">
+        <v>0</v>
+      </c>
+      <c r="S15" s="49">
+        <v>0</v>
+      </c>
+      <c r="T15" s="49">
+        <v>0</v>
+      </c>
+      <c r="U15" s="49">
+        <v>0</v>
+      </c>
+      <c r="V15" s="49">
+        <v>0</v>
+      </c>
+      <c r="W15" s="49">
+        <v>0</v>
+      </c>
+      <c r="X15" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="44">
-        <v>0</v>
-      </c>
-      <c r="C16" s="44">
-        <v>0</v>
-      </c>
-      <c r="D16" s="44">
-        <v>0</v>
-      </c>
-      <c r="E16" s="44">
-        <v>0</v>
-      </c>
-      <c r="F16" s="44">
-        <v>0</v>
-      </c>
-      <c r="G16" s="44">
-        <v>0</v>
-      </c>
-      <c r="H16" s="44">
-        <v>0</v>
-      </c>
-      <c r="I16" s="44">
-        <v>0</v>
-      </c>
-      <c r="J16" s="44">
-        <v>0</v>
-      </c>
-      <c r="K16" s="44">
-        <v>0</v>
-      </c>
-      <c r="L16" s="44">
-        <v>0</v>
-      </c>
-      <c r="M16" s="44">
-        <v>0</v>
-      </c>
-      <c r="N16" s="44">
-        <v>0</v>
-      </c>
-      <c r="O16" s="44">
-        <v>0</v>
-      </c>
-      <c r="P16" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="44">
-        <v>0</v>
-      </c>
-      <c r="R16" s="44">
-        <v>0</v>
-      </c>
-      <c r="S16" s="44">
-        <v>0</v>
-      </c>
-      <c r="T16" s="44">
-        <v>0</v>
-      </c>
-      <c r="U16" s="44">
-        <v>0</v>
-      </c>
-      <c r="V16" s="44">
-        <v>0</v>
-      </c>
-      <c r="W16" s="44">
-        <v>0</v>
-      </c>
-      <c r="X16" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY16" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="49">
+        <v>0</v>
+      </c>
+      <c r="C16" s="49">
+        <v>0</v>
+      </c>
+      <c r="D16" s="49">
+        <v>0</v>
+      </c>
+      <c r="E16" s="49">
+        <v>0</v>
+      </c>
+      <c r="F16" s="49">
+        <v>0</v>
+      </c>
+      <c r="G16" s="49">
+        <v>0</v>
+      </c>
+      <c r="H16" s="49">
+        <v>0</v>
+      </c>
+      <c r="I16" s="49">
+        <v>0</v>
+      </c>
+      <c r="J16" s="49">
+        <v>0</v>
+      </c>
+      <c r="K16" s="49">
+        <v>0</v>
+      </c>
+      <c r="L16" s="49">
+        <v>0</v>
+      </c>
+      <c r="M16" s="49">
+        <v>0</v>
+      </c>
+      <c r="N16" s="49">
+        <v>0</v>
+      </c>
+      <c r="O16" s="49">
+        <v>0</v>
+      </c>
+      <c r="P16" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="49">
+        <v>0</v>
+      </c>
+      <c r="R16" s="49">
+        <v>0</v>
+      </c>
+      <c r="S16" s="49">
+        <v>0</v>
+      </c>
+      <c r="T16" s="49">
+        <v>0</v>
+      </c>
+      <c r="U16" s="49">
+        <v>0</v>
+      </c>
+      <c r="V16" s="49">
+        <v>0</v>
+      </c>
+      <c r="W16" s="49">
+        <v>0</v>
+      </c>
+      <c r="X16" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="44">
-        <v>0</v>
-      </c>
-      <c r="C17" s="44">
-        <v>0</v>
-      </c>
-      <c r="D17" s="44">
-        <v>0</v>
-      </c>
-      <c r="E17" s="44">
-        <v>0</v>
-      </c>
-      <c r="F17" s="44">
-        <v>0</v>
-      </c>
-      <c r="G17" s="44">
-        <v>0</v>
-      </c>
-      <c r="H17" s="44">
-        <v>0</v>
-      </c>
-      <c r="I17" s="44">
-        <v>0</v>
-      </c>
-      <c r="J17" s="44">
-        <v>0</v>
-      </c>
-      <c r="K17" s="44">
-        <v>0</v>
-      </c>
-      <c r="L17" s="44">
-        <v>0</v>
-      </c>
-      <c r="M17" s="44">
-        <v>0</v>
-      </c>
-      <c r="N17" s="44">
-        <v>0</v>
-      </c>
-      <c r="O17" s="44">
-        <v>0</v>
-      </c>
-      <c r="P17" s="44">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="44">
-        <v>0</v>
-      </c>
-      <c r="R17" s="44">
-        <v>0</v>
-      </c>
-      <c r="S17" s="44">
-        <v>0</v>
-      </c>
-      <c r="T17" s="44">
-        <v>0</v>
-      </c>
-      <c r="U17" s="44">
-        <v>0</v>
-      </c>
-      <c r="V17" s="44">
-        <v>0</v>
-      </c>
-      <c r="W17" s="44">
-        <v>0</v>
-      </c>
-      <c r="X17" s="44">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AT17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AV17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AW17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AX17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AY17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B17" s="49">
+        <v>0</v>
+      </c>
+      <c r="C17" s="49">
+        <v>0</v>
+      </c>
+      <c r="D17" s="49">
+        <v>0</v>
+      </c>
+      <c r="E17" s="49">
+        <v>0</v>
+      </c>
+      <c r="F17" s="49">
+        <v>0</v>
+      </c>
+      <c r="G17" s="49">
+        <v>0</v>
+      </c>
+      <c r="H17" s="49">
+        <v>0</v>
+      </c>
+      <c r="I17" s="49">
+        <v>0</v>
+      </c>
+      <c r="J17" s="49">
+        <v>0</v>
+      </c>
+      <c r="K17" s="49">
+        <v>0</v>
+      </c>
+      <c r="L17" s="49">
+        <v>0</v>
+      </c>
+      <c r="M17" s="49">
+        <v>0</v>
+      </c>
+      <c r="N17" s="49">
+        <v>0</v>
+      </c>
+      <c r="O17" s="49">
+        <v>0</v>
+      </c>
+      <c r="P17" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="49">
+        <v>0</v>
+      </c>
+      <c r="R17" s="49">
+        <v>0</v>
+      </c>
+      <c r="S17" s="49">
+        <v>0</v>
+      </c>
+      <c r="T17" s="49">
+        <v>0</v>
+      </c>
+      <c r="U17" s="49">
+        <v>0</v>
+      </c>
+      <c r="V17" s="49">
+        <v>0</v>
+      </c>
+      <c r="W17" s="49">
+        <v>0</v>
+      </c>
+      <c r="X17" s="49">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="49">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="49">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -17379,4 +16389,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0336EC-8A0A-4AB4-82C3-9627454F5A78}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEF85D9F-0E08-450F-84A6-670EBF0A2B86}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2EAB8AD-5749-4C66-99DC-FBFEC9DC021B}"/>
 </file>